--- a/expData.xlsx
+++ b/expData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FCAC2B-6AF3-4A3D-B603-38E4AD9570C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE51890-6CCA-41FD-A287-CE985C7F9679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -5336,9 +5336,6 @@
     <t>What feeling do you get when you think you did something bad?</t>
   </si>
   <si>
-    <t>Guilty</t>
-  </si>
-  <si>
     <t>What emotion means being afraid to try again after many failures?</t>
   </si>
   <si>
@@ -6560,6 +6557,10 @@
   </si>
   <si>
     <t>What emotion describes deep sadness after losing something important?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guilty</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8539,7 +8540,7 @@
     </row>
     <row r="24" spans="2:6" ht="32.4">
       <c r="B24" s="8" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>534</v>
@@ -9221,7 +9222,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="C2" s="8" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>834</v>
@@ -11963,7 +11964,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -11980,7 +11981,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -12159,7 +12160,7 @@
         <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -13325,7 +13326,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>143</v>
@@ -14208,10 +14209,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -14274,10 +14275,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>2048</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>2049</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -14318,10 +14319,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>2066</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>2067</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -14343,7 +14344,7 @@
         <v>507</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -14431,7 +14432,7 @@
         <v>610</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -14442,7 +14443,7 @@
         <v>523</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -14497,7 +14498,7 @@
         <v>555</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -14508,7 +14509,7 @@
         <v>534</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -14574,7 +14575,7 @@
         <v>590</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -14585,7 +14586,7 @@
         <v>589</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -14615,10 +14616,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="12" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>2046</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -14648,10 +14649,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>2070</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -14714,10 +14715,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>2095</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>2096</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -14728,7 +14729,7 @@
         <v>611</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -14758,10 +14759,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>2092</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>2093</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -14802,10 +14803,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="8" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C56" s="8" t="s">
         <v>2078</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>2079</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -14816,7 +14817,7 @@
         <v>591</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -14934,10 +14935,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="8" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>2075</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -14956,10 +14957,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="8" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>2097</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>2098</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -14967,10 +14968,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="8" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C71" s="8" t="s">
         <v>2081</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>2082</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -15025,7 +15026,7 @@
         <v>622</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -15088,7 +15089,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C82" t="s">
         <v>228</v>
@@ -15308,10 +15309,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C102" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -15330,7 +15331,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C104" t="s">
         <v>265</v>
@@ -15352,7 +15353,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="C106" t="s">
         <v>268</v>
@@ -15385,10 +15386,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C109" t="s">
         <v>2085</v>
-      </c>
-      <c r="C109" t="s">
-        <v>2086</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -16208,7 +16209,7 @@
     </row>
     <row r="42" spans="2:8" ht="32.4">
       <c r="B42" s="8" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>1655</v>
@@ -16217,7 +16218,7 @@
         <v>1538</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>1652</v>
@@ -16225,16 +16226,16 @@
     </row>
     <row r="43" spans="2:8" ht="32.4">
       <c r="B43" s="8" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>1589</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>989</v>
@@ -16242,7 +16243,7 @@
     </row>
     <row r="44" spans="2:8" ht="32.4">
       <c r="B44" s="8" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>1661</v>
@@ -16259,16 +16260,16 @@
     </row>
     <row r="45" spans="2:8" ht="32.4">
       <c r="B45" s="8" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>2009</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>2010</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>1670</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>1655</v>
@@ -16276,7 +16277,7 @@
     </row>
     <row r="46" spans="2:8" ht="32.4">
       <c r="B46" s="8" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>1590</v>
@@ -16293,13 +16294,13 @@
     </row>
     <row r="47" spans="2:8" ht="32.4">
       <c r="B47" s="8" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>2013</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>2014</v>
-      </c>
       <c r="D47" s="8" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>1656</v>
@@ -16312,13 +16313,13 @@
     </row>
     <row r="48" spans="2:8" ht="32.4">
       <c r="B48" s="8" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>1652</v>
@@ -16331,7 +16332,7 @@
     </row>
     <row r="49" spans="2:8" ht="32.4">
       <c r="B49" s="8" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>1664</v>
@@ -16340,7 +16341,7 @@
         <v>1660</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>1659</v>
@@ -16350,13 +16351,13 @@
     </row>
     <row r="50" spans="2:8" ht="32.4">
       <c r="B50" s="8" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>1618</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>1665</v>
@@ -16369,13 +16370,13 @@
     </row>
     <row r="51" spans="2:8" ht="32.4">
       <c r="B51" s="8" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>1664</v>
@@ -16388,10 +16389,10 @@
     </row>
     <row r="52" spans="2:8" ht="32.4">
       <c r="B52" s="8" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>1658</v>
@@ -16400,14 +16401,14 @@
         <v>1672</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
     </row>
     <row r="53" spans="2:8" ht="32.4">
       <c r="B53" s="8" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>1671</v>
@@ -16416,7 +16417,7 @@
         <v>1662</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>1664</v>
@@ -16426,7 +16427,7 @@
     </row>
     <row r="54" spans="2:8" ht="32.4">
       <c r="B54" s="8" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>1663</v>
@@ -16435,7 +16436,7 @@
         <v>1671</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>1661</v>
@@ -16445,7 +16446,7 @@
     </row>
     <row r="55" spans="2:8" ht="32.4">
       <c r="B55" s="8" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>1671</v>
@@ -16464,32 +16465,32 @@
     </row>
     <row r="56" spans="2:8" ht="32.4">
       <c r="B56" s="8" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>1609</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>1574</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
     </row>
     <row r="57" spans="2:8" ht="32.4">
       <c r="B57" s="8" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>1662</v>
@@ -16502,7 +16503,7 @@
     </row>
     <row r="58" spans="2:8" ht="32.4">
       <c r="B58" s="8" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>1672</v>
@@ -16514,14 +16515,14 @@
         <v>1574</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
     <row r="59" spans="2:8" ht="32.4">
       <c r="B59" s="8" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>1655</v>
@@ -16540,19 +16541,19 @@
     </row>
     <row r="60" spans="2:8" ht="32.4">
       <c r="B60" s="8" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
@@ -16656,135 +16657,135 @@
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="8" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>1785</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>1786</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>1787</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>1788</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>1789</v>
       </c>
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="8" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>1790</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>1791</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>1791</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>1792</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>1793</v>
       </c>
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="8" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>1794</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>1795</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>1796</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>1797</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>1798</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="32.4">
       <c r="B5" s="8" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>1799</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="8" t="s">
         <v>1800</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>1801</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>1802</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="32.4">
       <c r="B6" s="8" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>1804</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>1805</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="32.4">
       <c r="B7" s="8" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>1807</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>1802</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>1787</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>1800</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>1808</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="32.4">
       <c r="B8" s="8" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>1809</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>1802</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>1810</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="32.4">
       <c r="B9" s="8" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>1800</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>1801</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>1651</v>
@@ -16792,24 +16793,24 @@
     </row>
     <row r="10" spans="2:6" ht="32.4">
       <c r="B10" s="8" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>1813</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>1793</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>1805</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>1814</v>
-      </c>
       <c r="F10" s="8" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="11" spans="2:6">
       <c r="B11" s="8" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>1651</v>
@@ -16818,188 +16819,188 @@
         <v>1539</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="12" spans="2:6">
       <c r="B12" s="8" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>1817</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>1786</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>1802</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>1810</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>1818</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="32.4">
       <c r="B13" s="8" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="D13" s="8" t="s">
+        <v>1819</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>1820</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="8" t="s">
         <v>1821</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>1822</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="32.4">
       <c r="B14" s="8" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="B15" s="8" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="32.4">
       <c r="B16" s="8" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>1786</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>1787</v>
-      </c>
       <c r="F16" s="8" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="32.4">
       <c r="B17" s="8" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>1827</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>1802</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>1828</v>
-      </c>
       <c r="E17" s="8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="32.4">
       <c r="B18" s="8" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="8" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="32.4">
       <c r="B20" s="8" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>1833</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>1820</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>1834</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>1821</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="32.4">
       <c r="B21" s="9" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>1539</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="32.4">
       <c r="B22" s="8" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>1539</v>
@@ -17008,106 +17009,106 @@
         <v>1651</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="32.4">
       <c r="B23" s="8" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1785</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>1844</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>1788</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>1786</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>1845</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="32.4">
       <c r="B24" s="8" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>1846</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>1847</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="E24" s="8" t="s">
         <v>1848</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="F24" s="8" t="s">
         <v>1849</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="32.4">
       <c r="B25" s="8" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="E25" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F25" s="8" t="s">
         <v>1801</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="32.4">
       <c r="B26" s="8" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="8" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="8" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>1539</v>
@@ -17115,33 +17116,33 @@
     </row>
     <row r="29" spans="2:6" ht="32.4">
       <c r="B29" s="8" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="32.4">
       <c r="B30" s="8" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>1540</v>
@@ -17149,101 +17150,101 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="8" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="D31" s="8" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>1786</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>1787</v>
-      </c>
       <c r="F31" s="8" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="8" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="32.4">
       <c r="B33" s="8" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="8" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="F34" s="8" t="s">
         <v>1863</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>1854</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>1800</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="35" spans="2:6" ht="32.4">
       <c r="B35" s="8" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="8" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>1655</v>
@@ -17251,67 +17252,67 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="8" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F37" s="8" t="s">
         <v>1867</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>1793</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>1800</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>1868</v>
       </c>
     </row>
     <row r="38" spans="2:6" ht="32.4">
       <c r="B38" s="8" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="8" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>1804</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>1871</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>1805</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>1788</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="32.4">
       <c r="B40" s="8" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="C40" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>1800</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>1802</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>1801</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>1538</v>
@@ -17319,186 +17320,186 @@
     </row>
     <row r="41" spans="2:6" s="11" customFormat="1">
       <c r="B41" s="9" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C41" s="9" t="s">
         <v>1874</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="D41" s="9" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>1875</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>1838</v>
-      </c>
-      <c r="E41" s="9" t="s">
+      <c r="F41" s="9" t="s">
         <v>1876</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="42" spans="2:6" ht="32.4">
       <c r="B42" s="8" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="43" spans="2:6" ht="32.4">
       <c r="B43" s="8" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>1880</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>1881</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="32.4">
       <c r="B44" s="8" t="s">
+        <v>1882</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>1883</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="D44" s="8" t="s">
         <v>1884</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="E44" s="8" t="s">
         <v>1885</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="F44" s="8" t="s">
         <v>1886</v>
-      </c>
-      <c r="F44" s="8" t="s">
-        <v>1887</v>
       </c>
     </row>
     <row r="45" spans="2:6" ht="32.4">
       <c r="B45" s="8" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>1838</v>
+      </c>
+      <c r="F45" s="8" t="s">
         <v>1888</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>1786</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>1839</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="32.4">
       <c r="B46" s="8" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>1819</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E46" s="8" t="s">
         <v>1890</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>1820</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>1834</v>
-      </c>
-      <c r="E46" s="8" t="s">
+      <c r="F46" s="8" t="s">
         <v>1891</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>1892</v>
       </c>
     </row>
     <row r="47" spans="2:6" ht="32.4">
       <c r="B47" s="8" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>1893</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="D47" s="8" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="F47" s="8" t="s">
         <v>1894</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>1796</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>1885</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>1895</v>
       </c>
     </row>
     <row r="48" spans="2:6" ht="32.4">
       <c r="B48" s="8" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>1896</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="D48" s="8" t="s">
         <v>1897</v>
       </c>
-      <c r="D48" s="8" t="s">
+      <c r="E48" s="8" t="s">
+        <v>1837</v>
+      </c>
+      <c r="F48" s="8" t="s">
         <v>1898</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>1838</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>1899</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="32.4">
       <c r="B49" s="8" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D49" s="8" t="s">
         <v>1900</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>1808</v>
-      </c>
-      <c r="D49" s="8" t="s">
+      <c r="E49" s="8" t="s">
         <v>1901</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="F49" s="8" t="s">
         <v>1902</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>1903</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="32.4">
       <c r="B50" s="8" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>1804</v>
+      </c>
+      <c r="F50" s="8" t="s">
         <v>1904</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>1788</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>1805</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>1905</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="32.4">
       <c r="B51" s="8" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>1906</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>1830</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>1840</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>1907</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>1669</v>
@@ -17506,172 +17507,172 @@
     </row>
     <row r="52" spans="2:6" ht="32.4">
       <c r="B52" s="8" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>1539</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>1909</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="53" spans="2:6" ht="32.4">
       <c r="B53" s="8" t="s">
-        <v>1910</v>
+        <v>1909</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>1651</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="32.4">
       <c r="B54" s="8" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>1912</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>1864</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>1842</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>1913</v>
-      </c>
       <c r="F54" s="8" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="32.4">
       <c r="B55" s="8" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C55" s="8" t="s">
         <v>1914</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="D55" s="8" t="s">
         <v>1915</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="E55" s="8" t="s">
         <v>1916</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="F55" s="8" t="s">
         <v>1917</v>
-      </c>
-      <c r="F55" s="8" t="s">
-        <v>1918</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="8" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>1802</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>1790</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>1919</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>1841</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>1803</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>1791</v>
-      </c>
-      <c r="F56" s="8" t="s">
-        <v>1920</v>
       </c>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="8" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E57" s="8" t="s">
         <v>1921</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>1795</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>1808</v>
-      </c>
-      <c r="E57" s="8" t="s">
+      <c r="F57" s="8" t="s">
         <v>1922</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="58" spans="2:6" ht="32.4">
       <c r="B58" s="8" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E58" s="8" t="s">
         <v>1924</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>1864</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>1802</v>
-      </c>
-      <c r="E58" s="8" t="s">
+      <c r="F58" s="8" t="s">
         <v>1925</v>
-      </c>
-      <c r="F58" s="8" t="s">
-        <v>1926</v>
       </c>
     </row>
     <row r="59" spans="2:6" ht="32.4">
       <c r="B59" s="8" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>1927</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="D59" s="8" t="s">
         <v>1928</v>
       </c>
-      <c r="D59" s="8" t="s">
+      <c r="E59" s="8" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F59" s="8" t="s">
         <v>1929</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>1915</v>
-      </c>
-      <c r="F59" s="8" t="s">
-        <v>1930</v>
       </c>
     </row>
     <row r="60" spans="2:6" ht="32.4">
       <c r="B60" s="8" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>1931</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="D60" s="8" t="s">
         <v>1932</v>
       </c>
-      <c r="D60" s="8" t="s">
+      <c r="E60" s="8" t="s">
         <v>1933</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="F60" s="8" t="s">
         <v>1934</v>
-      </c>
-      <c r="F60" s="8" t="s">
-        <v>1935</v>
       </c>
     </row>
     <row r="61" spans="2:6" ht="32.4">
       <c r="B61" s="8" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F61" s="8" t="s">
         <v>1936</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>1802</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>1787</v>
-      </c>
-      <c r="E61" s="8" t="s">
-        <v>1801</v>
-      </c>
-      <c r="F61" s="8" t="s">
-        <v>1937</v>
       </c>
     </row>
   </sheetData>
@@ -17720,7 +17721,7 @@
         <v>1681</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>1667</v>
+        <v>2101</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>1682</v>
@@ -17907,7 +17908,7 @@
         <v>1708</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>1704</v>
@@ -17924,7 +17925,7 @@
         <v>1710</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>1666</v>
@@ -17958,7 +17959,7 @@
         <v>1705</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>1698</v>
@@ -18009,7 +18010,7 @@
         <v>1691</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>1710</v>
@@ -18032,12 +18033,12 @@
         <v>1682</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>1730</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="32.4">
       <c r="B21" s="9" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>1700</v>
@@ -18049,29 +18050,29 @@
         <v>1682</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="32.4">
       <c r="B22" s="8" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>1685</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>1686</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="32.4">
       <c r="B23" s="8" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>1698</v>
@@ -18080,35 +18081,35 @@
         <v>1699</v>
       </c>
       <c r="E23" s="8" t="s">
+        <v>1736</v>
+      </c>
+      <c r="F23" s="8" t="s">
         <v>1737</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="32.4">
       <c r="B24" s="8" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>1710</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>1720</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="32.4">
       <c r="B25" s="8" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>1741</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>1742</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>1695</v>
@@ -18117,12 +18118,12 @@
         <v>1691</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="32.4">
       <c r="B26" s="8" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>1707</v>
@@ -18134,15 +18135,15 @@
         <v>1698</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="32.4">
       <c r="B27" s="8" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>1745</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>1746</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>1682</v>
@@ -18151,12 +18152,12 @@
         <v>1700</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="32.4">
       <c r="B28" s="8" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>1698</v>
@@ -18165,15 +18166,15 @@
         <v>1694</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="32.4">
       <c r="B29" s="8" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>1707</v>
@@ -18185,12 +18186,12 @@
         <v>1698</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="32.4">
       <c r="B30" s="8" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>1700</v>
@@ -18202,46 +18203,46 @@
         <v>1698</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="32.4">
       <c r="B31" s="8" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>1753</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>1979</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>1754</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>1701</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="8" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1721</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="32.4">
       <c r="B33" s="8" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>1700</v>
@@ -18250,7 +18251,7 @@
         <v>1682</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>1691</v>
@@ -18259,47 +18260,47 @@
     </row>
     <row r="34" spans="2:9" ht="32.4">
       <c r="B34" s="8" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="C34" s="8" t="s">
+        <v>1967</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>1968</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>1969</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>1682</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H34" s="8"/>
     </row>
     <row r="35" spans="2:9" ht="32.4">
       <c r="B35" s="8" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>1710</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="2:9" ht="32.4">
       <c r="B36" s="8" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>1761</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>1762</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>1688</v>
@@ -18308,13 +18309,13 @@
         <v>1686</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="2:9" ht="32.4">
       <c r="B37" s="8" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>1698</v>
@@ -18326,31 +18327,31 @@
         <v>1700</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="2:9" ht="32.4">
       <c r="B38" s="8" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="E38" s="8" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F38" s="8" t="s">
         <v>1766</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>1767</v>
       </c>
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="2:9" ht="32.4">
       <c r="B39" s="8" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>1682</v>
@@ -18362,31 +18363,31 @@
         <v>1698</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="2:9" ht="32.4">
       <c r="B40" s="8" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>1691</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="2:9" ht="32.4">
       <c r="B41" s="9" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>1698</v>
@@ -18398,88 +18399,88 @@
         <v>1707</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="2:9" ht="32.4">
       <c r="B42" s="8" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>1938</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="D42" s="8" t="s">
         <v>1939</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>1940</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>1698</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="2:9" ht="32.4">
       <c r="B43" s="8" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>1941</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>1942</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>1698</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="2:9" ht="32.4">
       <c r="B44" s="8" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>1688</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="2:9" ht="32.4">
       <c r="B45" s="8" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="2:9" ht="32.4">
       <c r="B46" s="8" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>1686</v>
@@ -18488,48 +18489,48 @@
         <v>1688</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="2:9" ht="32.4">
       <c r="B47" s="8" t="s">
+        <v>1946</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>1947</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>1948</v>
-      </c>
       <c r="D47" s="8" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>1703</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="I47" s="8"/>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="8" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>1949</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>1950</v>
-      </c>
       <c r="D48" s="8" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="32.4">
       <c r="B49" s="8" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>1688</v>
@@ -18538,197 +18539,197 @@
         <v>1686</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="32.4">
       <c r="B50" s="8" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>1698</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="32.4">
       <c r="B51" s="8" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>1996</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>1953</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>1997</v>
-      </c>
-      <c r="D51" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="E51" s="8" t="s">
-        <v>1955</v>
-      </c>
       <c r="F51" s="8" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="52" spans="2:6" ht="32.4">
       <c r="B52" s="8" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>1707</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="53" spans="2:6" ht="32.4">
       <c r="B53" s="8" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="E53" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F53" s="8" t="s">
         <v>1780</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="32.4">
       <c r="B54" s="8" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="32.4">
       <c r="B55" s="8" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>1985</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>1959</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>1986</v>
-      </c>
-      <c r="D55" s="8" t="s">
+      <c r="E55" s="8" t="s">
         <v>1960</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>1961</v>
-      </c>
       <c r="F55" s="8" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="8" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>1712</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="57" spans="2:6" ht="32.4">
       <c r="B57" s="8" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E57" s="8" t="s">
         <v>1963</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="F57" s="8" t="s">
         <v>1998</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>2000</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>1964</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>1999</v>
       </c>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="8" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="59" spans="2:6" ht="32.4">
       <c r="B59" s="8" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>1688</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="60" spans="2:6" ht="32.4">
       <c r="B60" s="8" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
   </sheetData>
@@ -19001,7 +19002,7 @@
         <v>643</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>48</v>
@@ -19021,13 +19022,13 @@
         <v>85</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>92</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -19038,10 +19039,10 @@
         <v>645</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>49</v>
@@ -19064,7 +19065,7 @@
         <v>88</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>630</v>
@@ -19095,19 +19096,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32.4">
@@ -19121,7 +19122,7 @@
         <v>56</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>71</v>

--- a/expData.xlsx
+++ b/expData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE51890-6CCA-41FD-A287-CE985C7F9679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C284FF7F-49D8-482D-8C02-DA0E90C9B29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3259" uniqueCount="2102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3259" uniqueCount="2103">
   <si>
     <t>activeScence</t>
   </si>
@@ -5996,9 +5996,6 @@
     <t>Happiness</t>
   </si>
   <si>
-    <t>What word means strong love, loyalty, or dedication to someone or something?</t>
-  </si>
-  <si>
     <t>What word describes the state of refusing to believe something?</t>
   </si>
   <si>
@@ -6246,9 +6243,6 @@
     <t>What word means a formal test of knowledge or ability?</t>
   </si>
   <si>
-    <t>What word describes someone who has completed their studies at a school?</t>
-  </si>
-  <si>
     <t>Lecturer</t>
   </si>
   <si>
@@ -6329,10 +6323,6 @@
   </si>
   <si>
     <t>Enroll</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>What word means 「to become eligible for something by achieving certain standards」?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6561,6 +6551,22 @@
   </si>
   <si>
     <t>Guilty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boredom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>What word means loyalty, and dedication to someone or something?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>What word means 「to meet the requirements for something」?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>What word means a person who has completed their studies?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8540,7 +8546,7 @@
     </row>
     <row r="24" spans="2:6" ht="32.4">
       <c r="B24" s="8" t="s">
-        <v>2061</v>
+        <v>2058</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>534</v>
@@ -9222,7 +9228,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="C2" s="8" t="s">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>834</v>
@@ -11964,7 +11970,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>2050</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -11981,7 +11987,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>2051</v>
+        <v>2048</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -12160,7 +12166,7 @@
         <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -13326,7 +13332,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>2089</v>
+        <v>2086</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>143</v>
@@ -14209,10 +14215,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>2071</v>
+        <v>2068</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>2063</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -14275,10 +14281,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>2047</v>
+        <v>2044</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>2048</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -14319,10 +14325,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>2065</v>
+        <v>2062</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>2066</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -14344,7 +14350,7 @@
         <v>507</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>2093</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -14432,7 +14438,7 @@
         <v>610</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -14443,7 +14449,7 @@
         <v>523</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>2064</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -14498,7 +14504,7 @@
         <v>555</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>2049</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -14509,7 +14515,7 @@
         <v>534</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>2090</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -14575,7 +14581,7 @@
         <v>590</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>2067</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -14586,7 +14592,7 @@
         <v>589</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>2068</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -14616,10 +14622,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>2045</v>
+        <v>2042</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>2046</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -14649,10 +14655,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>2069</v>
+        <v>2066</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>2070</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -14715,10 +14721,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>2094</v>
+        <v>2091</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>2095</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -14729,7 +14735,7 @@
         <v>611</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -14759,10 +14765,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>2092</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -14803,10 +14809,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>2077</v>
+        <v>2074</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -14817,7 +14823,7 @@
         <v>591</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>2079</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -14935,10 +14941,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>2074</v>
+        <v>2071</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>2075</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -14957,10 +14963,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>2096</v>
+        <v>2093</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>2097</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -14968,10 +14974,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -15026,7 +15032,7 @@
         <v>622</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>2076</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -15089,7 +15095,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>2082</v>
+        <v>2079</v>
       </c>
       <c r="C82" t="s">
         <v>228</v>
@@ -15309,10 +15315,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C102" t="s">
-        <v>2083</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -15331,7 +15337,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C104" t="s">
         <v>265</v>
@@ -15353,7 +15359,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
       <c r="C106" t="s">
         <v>268</v>
@@ -15386,10 +15392,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>2084</v>
+        <v>2081</v>
       </c>
       <c r="C109" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -16209,7 +16215,7 @@
     </row>
     <row r="42" spans="2:8" ht="32.4">
       <c r="B42" s="8" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>1655</v>
@@ -16218,7 +16224,7 @@
         <v>1538</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>1652</v>
@@ -16226,16 +16232,16 @@
     </row>
     <row r="43" spans="2:8" ht="32.4">
       <c r="B43" s="8" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>1589</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>989</v>
@@ -16243,7 +16249,7 @@
     </row>
     <row r="44" spans="2:8" ht="32.4">
       <c r="B44" s="8" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>1661</v>
@@ -16260,16 +16266,16 @@
     </row>
     <row r="45" spans="2:8" ht="32.4">
       <c r="B45" s="8" t="s">
+        <v>2007</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>2008</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>2009</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>1670</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>1655</v>
@@ -16277,7 +16283,7 @@
     </row>
     <row r="46" spans="2:8" ht="32.4">
       <c r="B46" s="8" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>1590</v>
@@ -16294,13 +16300,13 @@
     </row>
     <row r="47" spans="2:8" ht="32.4">
       <c r="B47" s="8" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>2012</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>2013</v>
-      </c>
       <c r="D47" s="8" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>1656</v>
@@ -16313,13 +16319,13 @@
     </row>
     <row r="48" spans="2:8" ht="32.4">
       <c r="B48" s="8" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>1652</v>
@@ -16332,7 +16338,7 @@
     </row>
     <row r="49" spans="2:8" ht="32.4">
       <c r="B49" s="8" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>1664</v>
@@ -16341,7 +16347,7 @@
         <v>1660</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>1659</v>
@@ -16351,13 +16357,13 @@
     </row>
     <row r="50" spans="2:8" ht="32.4">
       <c r="B50" s="8" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>1618</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>1665</v>
@@ -16370,13 +16376,13 @@
     </row>
     <row r="51" spans="2:8" ht="32.4">
       <c r="B51" s="8" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>1664</v>
@@ -16389,10 +16395,10 @@
     </row>
     <row r="52" spans="2:8" ht="32.4">
       <c r="B52" s="8" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>1658</v>
@@ -16401,14 +16407,14 @@
         <v>1672</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
     </row>
     <row r="53" spans="2:8" ht="32.4">
       <c r="B53" s="8" t="s">
-        <v>2020</v>
+        <v>2102</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>1671</v>
@@ -16417,7 +16423,7 @@
         <v>1662</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>1664</v>
@@ -16427,7 +16433,7 @@
     </row>
     <row r="54" spans="2:8" ht="32.4">
       <c r="B54" s="8" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>1663</v>
@@ -16436,7 +16442,7 @@
         <v>1671</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>1661</v>
@@ -16446,7 +16452,7 @@
     </row>
     <row r="55" spans="2:8" ht="32.4">
       <c r="B55" s="8" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>1671</v>
@@ -16465,32 +16471,32 @@
     </row>
     <row r="56" spans="2:8" ht="32.4">
       <c r="B56" s="8" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>1609</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>1574</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
     </row>
     <row r="57" spans="2:8" ht="32.4">
       <c r="B57" s="8" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>1662</v>
@@ -16503,7 +16509,7 @@
     </row>
     <row r="58" spans="2:8" ht="32.4">
       <c r="B58" s="8" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>1672</v>
@@ -16515,14 +16521,14 @@
         <v>1574</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
     <row r="59" spans="2:8" ht="32.4">
       <c r="B59" s="8" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>1655</v>
@@ -16541,19 +16547,19 @@
     </row>
     <row r="60" spans="2:8" ht="32.4">
       <c r="B60" s="8" t="s">
-        <v>2044</v>
+        <v>2101</v>
       </c>
       <c r="C60" s="8" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E60" s="8" t="s">
         <v>2040</v>
       </c>
-      <c r="D60" s="8" t="s">
-        <v>2043</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>2042</v>
-      </c>
       <c r="F60" s="8" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
@@ -17721,7 +17727,7 @@
         <v>1681</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>1682</v>
@@ -17908,7 +17914,7 @@
         <v>1708</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>1704</v>
@@ -17925,7 +17931,7 @@
         <v>1710</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>1666</v>
@@ -17959,7 +17965,7 @@
         <v>1705</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>1698</v>
@@ -18010,7 +18016,7 @@
         <v>1691</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>1710</v>
@@ -18033,7 +18039,7 @@
         <v>1682</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>2101</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="32.4">
@@ -18095,7 +18101,7 @@
         <v>1710</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>1720</v>
@@ -18166,7 +18172,7 @@
         <v>1694</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>1748</v>
@@ -18211,7 +18217,7 @@
         <v>1752</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>1753</v>
@@ -18228,16 +18234,16 @@
         <v>1755</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>1721</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="32.4">
@@ -18251,7 +18257,7 @@
         <v>1682</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>1691</v>
@@ -18263,16 +18269,16 @@
         <v>1757</v>
       </c>
       <c r="C34" s="8" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>1967</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>1968</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>1682</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H34" s="8"/>
     </row>
@@ -18281,10 +18287,10 @@
         <v>1758</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>1710</v>
@@ -18315,7 +18321,7 @@
     </row>
     <row r="37" spans="2:9" ht="32.4">
       <c r="B37" s="8" t="s">
-        <v>2099</v>
+        <v>2096</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>1698</v>
@@ -18333,13 +18339,13 @@
     </row>
     <row r="38" spans="2:9" ht="32.4">
       <c r="B38" s="8" t="s">
-        <v>2100</v>
+        <v>2097</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>1765</v>
@@ -18372,16 +18378,16 @@
         <v>1769</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>1691</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="I40" s="8"/>
     </row>
@@ -18417,7 +18423,7 @@
         <v>1698</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="I42" s="8"/>
     </row>
@@ -18435,7 +18441,7 @@
         <v>1743</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="I43" s="8"/>
     </row>
@@ -18444,7 +18450,7 @@
         <v>1942</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>1688</v>
@@ -18453,7 +18459,7 @@
         <v>1943</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="I44" s="8"/>
     </row>
@@ -18501,13 +18507,13 @@
         <v>1947</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>1703</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="I47" s="8"/>
     </row>
@@ -18530,7 +18536,7 @@
     </row>
     <row r="49" spans="2:6" ht="32.4">
       <c r="B49" s="8" t="s">
-        <v>1950</v>
+        <v>2100</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>1688</v>
@@ -18539,41 +18545,41 @@
         <v>1686</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>1774</v>
+        <v>2099</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="32.4">
       <c r="B50" s="8" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>1698</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="32.4">
       <c r="B51" s="8" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>1952</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>1996</v>
-      </c>
-      <c r="D51" s="8" t="s">
+      <c r="E51" s="8" t="s">
         <v>1953</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>1954</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>1777</v>
@@ -18581,13 +18587,13 @@
     </row>
     <row r="52" spans="2:6" ht="32.4">
       <c r="B52" s="8" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>1707</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>1745</v>
@@ -18598,13 +18604,13 @@
     </row>
     <row r="53" spans="2:6" ht="32.4">
       <c r="B53" s="8" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>1779</v>
@@ -18615,84 +18621,84 @@
     </row>
     <row r="54" spans="2:6" ht="32.4">
       <c r="B54" s="8" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>1773</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="32.4">
       <c r="B55" s="8" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>1984</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>1958</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>1985</v>
-      </c>
-      <c r="D55" s="8" t="s">
+      <c r="E55" s="8" t="s">
         <v>1959</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>1960</v>
-      </c>
       <c r="F55" s="8" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="8" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>1772</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>1712</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="57" spans="2:6" ht="32.4">
       <c r="B57" s="8" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>1996</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E57" s="8" t="s">
         <v>1962</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="F57" s="8" t="s">
         <v>1997</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>1999</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>1963</v>
-      </c>
-      <c r="F57" s="8" t="s">
-        <v>1998</v>
       </c>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="8" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>1782</v>
@@ -18700,7 +18706,7 @@
     </row>
     <row r="59" spans="2:6" ht="32.4">
       <c r="B59" s="8" t="s">
-        <v>2098</v>
+        <v>2095</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>1688</v>
@@ -18717,19 +18723,19 @@
     </row>
     <row r="60" spans="2:6" ht="32.4">
       <c r="B60" s="8" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
   </sheetData>
@@ -19002,7 +19008,7 @@
         <v>643</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>48</v>
@@ -19022,13 +19028,13 @@
         <v>85</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>2059</v>
+        <v>2056</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>92</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -19039,10 +19045,10 @@
         <v>645</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>2053</v>
+        <v>2050</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>2058</v>
+        <v>2055</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>49</v>
@@ -19065,7 +19071,7 @@
         <v>88</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>2057</v>
+        <v>2054</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>630</v>
@@ -19096,19 +19102,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>2056</v>
+        <v>2053</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>2060</v>
+        <v>2057</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>2055</v>
+        <v>2052</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>73</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>2054</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32.4">
@@ -19122,7 +19128,7 @@
         <v>56</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>2052</v>
+        <v>2049</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>71</v>

--- a/expData.xlsx
+++ b/expData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\e\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F2CA7B-AA86-4809-8714-BD00A20E2177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B435A2F-AD65-490B-9A1A-AEF176DB28F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4961,7 +4961,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="4">
-        <v>15</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="3" spans="1:5">

--- a/expData.xlsx
+++ b/expData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{052A469D-2646-42EF-A9F6-F0F3DBD653F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D2C3AF-BAA0-4D64-8487-212F935F5A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="1491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="1508">
   <si>
     <t>activeScence</t>
   </si>
@@ -2819,9 +2819,6 @@
     <t>Survey</t>
   </si>
   <si>
-    <t>Profile</t>
-  </si>
-  <si>
     <t>Application</t>
   </si>
   <si>
@@ -2852,9 +2849,6 @@
     <t>What is a document showing someone has finished a course?</t>
   </si>
   <si>
-    <t>Card</t>
-  </si>
-  <si>
     <t>License</t>
   </si>
   <si>
@@ -2960,9 +2954,6 @@
     <t>Curious</t>
   </si>
   <si>
-    <t>Knowledgeable</t>
-  </si>
-  <si>
     <t>Dormitory</t>
   </si>
   <si>
@@ -4077,10 +4068,6 @@
   </si>
   <si>
     <t>Lecture</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Study</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4857,6 +4844,90 @@
   </si>
   <si>
     <t>吸引人的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ruler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>semester</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Semester</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subject</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quiz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quiz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kindergarten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>English</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kindergarten</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Textbook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mandarin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Math</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>History</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Review</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Essay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Definition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Academy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Knowledgeable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Educate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Curriculum</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5296,7 +5367,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -5352,7 +5423,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E5" s="4" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
     </row>
   </sheetData>
@@ -5445,7 +5516,7 @@
         <v>145</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>153</v>
@@ -5485,7 +5556,7 @@
         <v>145</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>126</v>
@@ -5511,7 +5582,7 @@
         <v>151</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -5585,7 +5656,7 @@
         <v>114</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>132</v>
@@ -5602,7 +5673,7 @@
         <v>716</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>120</v>
@@ -5722,7 +5793,7 @@
         <v>722</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>149</v>
@@ -5742,7 +5813,7 @@
         <v>711</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>131</v>
@@ -5766,10 +5837,10 @@
         <v>149</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>147</v>
@@ -5889,7 +5960,7 @@
         <v>689</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>413</v>
@@ -5916,7 +5987,7 @@
         <v>682</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>445</v>
@@ -5930,13 +6001,13 @@
         <v>692</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>425</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>64</v>
@@ -5987,7 +6058,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>686</v>
@@ -5996,7 +6067,7 @@
         <v>457</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>411</v>
@@ -6053,7 +6124,7 @@
         <v>682</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>433</v>
@@ -6070,7 +6141,7 @@
         <v>698</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>429</v>
@@ -6093,10 +6164,10 @@
         <v>460</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>419</v>
@@ -6233,7 +6304,7 @@
         <v>130</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>429</v>
@@ -6550,7 +6621,7 @@
         <v>742</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>682</v>
@@ -6638,7 +6709,7 @@
         <v>281</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -6646,19 +6717,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="C2" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -6666,19 +6737,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>1429</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>1433</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -6686,19 +6757,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>1434</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>1438</v>
-      </c>
       <c r="D4" s="7" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -6706,19 +6777,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6726,16 +6797,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>530</v>
@@ -6746,19 +6817,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -6766,19 +6837,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -6786,19 +6857,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>1450</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>1454</v>
-      </c>
       <c r="D9" s="7" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="G9" s="7"/>
     </row>
@@ -6807,19 +6878,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>1431</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>1433</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>1435</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -6828,13 +6899,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>532</v>
@@ -6849,19 +6920,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="G12" s="7"/>
     </row>
@@ -6870,19 +6941,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>530</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="G13" s="7"/>
     </row>
@@ -6891,19 +6962,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>583</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="G14" s="7"/>
     </row>
@@ -6912,19 +6983,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>587</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="G15" s="7"/>
     </row>
@@ -6933,19 +7004,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>586</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>563</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="G16" s="7"/>
     </row>
@@ -6954,19 +7025,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="G17" s="7"/>
     </row>
@@ -6975,19 +7046,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>275</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -6995,16 +7066,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>566</v>
@@ -7015,19 +7086,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>587</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>586</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -7035,19 +7106,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -7058,16 +7129,16 @@
         <v>745</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>520</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -7078,7 +7149,7 @@
         <v>746</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>491</v>
@@ -7095,7 +7166,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>511</v>
@@ -7135,7 +7206,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>274</v>
@@ -7144,7 +7215,7 @@
         <v>532</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>478</v>
@@ -7195,7 +7266,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>491</v>
@@ -7418,7 +7489,7 @@
         <v>761</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>520</v>
@@ -7439,7 +7510,7 @@
         <v>762</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>516</v>
@@ -7460,7 +7531,7 @@
         <v>763</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>491</v>
@@ -7586,7 +7657,7 @@
         <v>773</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>514</v>
@@ -7628,7 +7699,7 @@
         <v>777</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>491</v>
@@ -7715,13 +7786,13 @@
         <v>784</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="G54" s="7"/>
     </row>
@@ -7733,7 +7804,7 @@
         <v>785</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>509</v>
@@ -7742,7 +7813,7 @@
         <v>524</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="G55" s="7"/>
     </row>
@@ -7777,13 +7848,13 @@
         <v>520</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>509</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -7794,7 +7865,7 @@
         <v>788</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>514</v>
@@ -8012,7 +8083,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -8021,7 +8092,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -8038,7 +8109,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -8052,7 +8123,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -8217,7 +8288,7 @@
         <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -9273,7 +9344,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>123</v>
@@ -9317,10 +9388,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -9328,10 +9399,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -9339,7 +9410,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>133</v>
@@ -9372,7 +9443,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>138</v>
@@ -9394,7 +9465,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>141</v>
@@ -9405,7 +9476,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>142</v>
@@ -9559,7 +9630,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>444</v>
@@ -9625,7 +9696,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>158</v>
@@ -9636,7 +9707,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>415</v>
@@ -9911,7 +9982,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>295</v>
@@ -9947,7 +10018,7 @@
         <v>300</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
@@ -10120,7 +10191,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>332</v>
@@ -10153,7 +10224,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>336</v>
@@ -10186,7 +10257,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>341</v>
@@ -10233,10 +10304,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -10299,10 +10370,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -10332,10 +10403,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -10357,7 +10428,7 @@
         <v>484</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -10445,7 +10516,7 @@
         <v>585</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
@@ -10456,7 +10527,7 @@
         <v>500</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -10511,7 +10582,7 @@
         <v>532</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -10522,7 +10593,7 @@
         <v>511</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -10588,7 +10659,7 @@
         <v>566</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -10599,7 +10670,7 @@
         <v>565</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -10629,10 +10700,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
@@ -10662,10 +10733,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -10684,10 +10755,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -10728,10 +10799,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -10742,7 +10813,7 @@
         <v>586</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -10772,10 +10843,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
@@ -10816,10 +10887,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -10937,10 +11008,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
@@ -10959,10 +11030,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -10970,10 +11041,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -11028,7 +11099,7 @@
         <v>597</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -11091,7 +11162,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C80" t="s">
         <v>221</v>
@@ -11157,7 +11228,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="C86" t="s">
         <v>233</v>
@@ -11270,7 +11341,7 @@
         <v>247</v>
       </c>
       <c r="C96" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -11300,10 +11371,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>1264</v>
+        <v>1261</v>
       </c>
       <c r="C99" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -11322,7 +11393,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="C101" t="s">
         <v>254</v>
@@ -11344,7 +11415,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="C103" t="s">
         <v>257</v>
@@ -11377,10 +11448,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C106" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -11399,7 +11470,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="C108" t="s">
         <v>263</v>
@@ -11413,7 +11484,7 @@
         <v>463</v>
       </c>
       <c r="C109" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -11424,7 +11495,7 @@
         <v>264</v>
       </c>
       <c r="C110" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -11435,7 +11506,7 @@
         <v>265</v>
       </c>
       <c r="C111" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -11496,9 +11567,10 @@
   <cols>
     <col min="2" max="2" width="38.88671875" customWidth="1"/>
     <col min="3" max="6" width="22" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>25</v>
       </c>
@@ -11518,7 +11590,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
         <v>802</v>
       </c>
@@ -11535,7 +11607,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
         <v>806</v>
       </c>
@@ -11551,8 +11623,11 @@
       <c r="F3" s="7" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="H3" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>811</v>
       </c>
@@ -11568,8 +11643,11 @@
       <c r="F4" s="7" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="H4" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>816</v>
       </c>
@@ -11585,8 +11663,11 @@
       <c r="F5" s="7" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H5" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
         <v>821</v>
       </c>
@@ -11602,8 +11683,11 @@
       <c r="F6" s="7" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H6" s="3" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>825</v>
       </c>
@@ -11614,13 +11698,16 @@
         <v>803</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>804</v>
+        <v>1489</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H7" s="3" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
         <v>827</v>
       </c>
@@ -11636,8 +11723,11 @@
       <c r="F8" s="7" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H8" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
         <v>832</v>
       </c>
@@ -11645,7 +11735,7 @@
         <v>804</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>805</v>
+        <v>1498</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>826</v>
@@ -11653,13 +11743,16 @@
       <c r="F9" s="7" t="s">
         <v>803</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H9" s="3" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>833</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>40</v>
+        <v>1494</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>834</v>
@@ -11670,8 +11763,9 @@
       <c r="F10" s="7" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
         <v>836</v>
       </c>
@@ -11682,13 +11776,16 @@
         <v>813</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>837</v>
+        <v>1500</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="H11" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
         <v>838</v>
       </c>
@@ -11704,8 +11801,11 @@
       <c r="F12" s="7" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H12" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
         <v>839</v>
       </c>
@@ -11721,13 +11821,16 @@
       <c r="F13" s="7" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="H13" s="3" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
         <v>841</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>805</v>
+        <v>1495</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>803</v>
@@ -11738,8 +11841,11 @@
       <c r="F14" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="H14" s="3" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
         <v>842</v>
       </c>
@@ -11747,7 +11853,7 @@
         <v>843</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>844</v>
+        <v>1496</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>845</v>
@@ -11755,8 +11861,11 @@
       <c r="F15" s="7" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="H15" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>847</v>
       </c>
@@ -11770,15 +11879,18 @@
         <v>840</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+        <v>1496</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>849</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>805</v>
+        <v>1492</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>804</v>
@@ -11789,8 +11901,11 @@
       <c r="F17" s="7" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="H17" s="3" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>851</v>
       </c>
@@ -11806,10 +11921,13 @@
       <c r="F18" s="7" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="H18" s="3" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>812</v>
@@ -11824,15 +11942,15 @@
         <v>843</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
         <v>855</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>804</v>
+        <v>1500</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>805</v>
+        <v>1499</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>826</v>
@@ -11841,7 +11959,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="2:6" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
         <v>856</v>
       </c>
@@ -11858,7 +11976,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="22" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
         <v>857</v>
       </c>
@@ -11875,7 +11993,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
         <v>862</v>
       </c>
@@ -11892,9 +12010,9 @@
         <v>865</v>
       </c>
     </row>
-    <row r="24" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>844</v>
@@ -11909,7 +12027,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="25" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
         <v>869</v>
       </c>
@@ -11926,12 +12044,12 @@
         <v>873</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
         <v>874</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>859</v>
+        <v>1501</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>867</v>
@@ -11943,9 +12061,9 @@
         <v>875</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>826</v>
@@ -11960,7 +12078,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="28" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
         <v>877</v>
       </c>
@@ -11977,7 +12095,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="29" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
         <v>882</v>
       </c>
@@ -11994,9 +12112,9 @@
         <v>885</v>
       </c>
     </row>
-    <row r="30" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>886</v>
@@ -12011,7 +12129,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="31" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
         <v>888</v>
       </c>
@@ -12019,18 +12137,18 @@
         <v>889</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>859</v>
+        <v>1501</v>
       </c>
       <c r="E31" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>890</v>
       </c>
-      <c r="F31" s="7" t="s">
+    </row>
+    <row r="32" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
+      <c r="B32" s="7" t="s">
         <v>891</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
-      <c r="B32" s="7" t="s">
-        <v>892</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>867</v>
@@ -12039,24 +12157,24 @@
         <v>885</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>868</v>
+        <v>1503</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>894</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>895</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="E33" s="7" t="s">
         <v>896</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>897</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>798</v>
@@ -12064,10 +12182,10 @@
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>865</v>
@@ -12076,21 +12194,21 @@
         <v>863</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>901</v>
+        <v>1502</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>867</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>878</v>
@@ -12098,10 +12216,10 @@
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>803</v>
@@ -12110,21 +12228,21 @@
         <v>826</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>861</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>858</v>
@@ -12132,41 +12250,41 @@
     </row>
     <row r="38" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C38" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>909</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="F38" s="7" t="s">
         <v>910</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B39" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>850</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B40" s="7" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>884</v>
@@ -12175,7 +12293,7 @@
         <v>885</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>859</v>
+        <v>1503</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>883</v>
@@ -12183,7 +12301,7 @@
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="8" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>803</v>
@@ -12192,41 +12310,41 @@
         <v>826</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
-        <v>1268</v>
+        <v>1265</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>807</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>921</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>1269</v>
+        <v>1266</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>858</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>799</v>
@@ -12234,124 +12352,124 @@
     </row>
     <row r="44" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
-        <v>1270</v>
+        <v>1267</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>940</v>
+        <v>1290</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B45" s="7" t="s">
-        <v>1271</v>
+        <v>1268</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>1272</v>
+        <v>1269</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>1273</v>
+        <v>1270</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>859</v>
+        <v>1504</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>878</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>1276</v>
+        <v>1273</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
     <row r="48" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B49" s="7" t="s">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
     </row>
     <row r="50" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B50" s="7" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>887</v>
+        <v>1297</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>873</v>
@@ -12361,190 +12479,190 @@
     </row>
     <row r="51" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
     </row>
     <row r="52" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
-        <v>1282</v>
+        <v>1279</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
     </row>
     <row r="53" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>940</v>
+        <v>1505</v>
       </c>
       <c r="D53" s="7" t="s">
+        <v>929</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>931</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>1284</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>933</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
     </row>
     <row r="54" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1298</v>
+        <v>1507</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
     </row>
     <row r="55" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
     </row>
     <row r="56" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>878</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>843</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
     </row>
     <row r="57" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>937</v>
+        <v>1505</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
     </row>
     <row r="58" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>843</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
     </row>
     <row r="59" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B59" s="7" t="s">
-        <v>1292</v>
+        <v>1289</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>921</v>
+        <v>1506</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
     </row>
     <row r="60" spans="2:8" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -12654,19 +12772,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>1056</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>1057</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -12674,19 +12792,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>808</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -12694,19 +12812,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>1065</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>1066</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -12714,19 +12832,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>1070</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>1392</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>1073</v>
-      </c>
       <c r="F5" s="7" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="G5" s="3"/>
     </row>
@@ -12735,19 +12853,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -12756,19 +12874,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="G7" s="3"/>
     </row>
@@ -12777,19 +12895,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -12797,19 +12915,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -12817,19 +12935,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -12837,19 +12955,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -12857,19 +12975,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -12877,19 +12995,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>918</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>1090</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>920</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -12897,19 +13015,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -12917,19 +13035,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -12937,19 +13055,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -12957,19 +13075,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -12977,19 +13095,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>808</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -12997,19 +13115,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>707</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -13017,19 +13135,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -13037,19 +13155,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -13057,19 +13175,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>808</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -13077,19 +13195,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -13097,19 +13215,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>1116</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>1117</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -13117,19 +13235,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -13137,19 +13255,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -13157,19 +13275,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>808</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -13177,16 +13295,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>808</v>
@@ -13197,19 +13315,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -13217,16 +13335,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>809</v>
@@ -13237,19 +13355,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -13257,19 +13375,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -13277,19 +13395,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -13297,19 +13415,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -13317,19 +13435,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F35" s="7" t="s">
         <v>1059</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -13337,19 +13455,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -13357,19 +13475,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -13377,19 +13495,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>808</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -13397,19 +13515,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -13417,16 +13535,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>807</v>
@@ -13437,19 +13555,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F41" s="8" t="s">
         <v>1144</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>1108</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -13457,19 +13575,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -13477,19 +13595,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="32.4" x14ac:dyDescent="0.3">
@@ -13497,19 +13615,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="G44" s="3"/>
     </row>
@@ -13518,19 +13636,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="G45" s="3"/>
     </row>
@@ -13539,19 +13657,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="G46" s="3"/>
     </row>
@@ -13560,19 +13678,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="G47" s="3"/>
     </row>
@@ -13581,19 +13699,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>1161</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>1164</v>
       </c>
       <c r="G48" s="3"/>
     </row>
@@ -13602,19 +13720,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>1165</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>1166</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>1168</v>
       </c>
       <c r="G49" s="3"/>
     </row>
@@ -13623,19 +13741,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -13645,19 +13763,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="H51" s="3"/>
     </row>
@@ -13666,19 +13784,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="H52" s="3"/>
     </row>
@@ -13687,19 +13805,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="H53" s="3"/>
     </row>
@@ -13708,19 +13826,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="H54" s="3"/>
     </row>
@@ -13729,19 +13847,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>1407</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>1179</v>
-      </c>
       <c r="F55" s="7" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="H55" s="3"/>
     </row>
@@ -13750,19 +13868,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="H56" s="3"/>
     </row>
@@ -13771,19 +13889,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="H57" s="3"/>
     </row>
@@ -13792,19 +13910,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="H58" s="3"/>
     </row>
@@ -13813,19 +13931,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
@@ -13833,19 +13951,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E60" s="7" t="s">
         <v>1192</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="F60" s="7" t="s">
         <v>1193</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>1194</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="32.4" x14ac:dyDescent="0.3">
@@ -13853,19 +13971,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
     </row>
   </sheetData>
@@ -13909,1021 +14027,1021 @@
     </row>
     <row r="2" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B2" s="7" t="s">
+        <v>946</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>947</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>948</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>949</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>950</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>951</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
+        <v>950</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>952</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>953</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>954</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>955</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>956</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
+        <v>955</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>956</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>958</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>959</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>935</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>960</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
+        <v>959</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>962</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>963</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>964</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>965</v>
-      </c>
       <c r="F5" s="7" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>964</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>965</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>966</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>967</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>968</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>969</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
+        <v>968</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>969</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>971</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>972</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>935</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>973</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B8" s="7" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B11" s="7" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B12" s="7" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B13" s="7" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B14" s="7" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B15" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>986</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>987</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>988</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>960</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>989</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>990</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1245</v>
+        <v>1242</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B19" s="7" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B20" s="7" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B23" s="7" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B24" s="7" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1236</v>
+        <v>1233</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B25" s="7" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>976</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>979</v>
-      </c>
       <c r="E26" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B27" s="7" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B28" s="7" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1242</v>
+        <v>1239</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B29" s="7" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B31" s="7" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="7" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>1233</v>
+        <v>1230</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B33" s="7" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="H33" s="7"/>
     </row>
     <row r="34" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B34" s="7" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="H34" s="7"/>
     </row>
     <row r="35" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B35" s="7" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B36" s="7" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B37" s="7" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B38" s="7" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>1035</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>1236</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>1239</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>1038</v>
       </c>
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B39" s="7" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B40" s="7" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C40" s="7" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>1237</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>1240</v>
-      </c>
       <c r="E40" s="7" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B41" s="8" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B42" s="7" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B44" s="7" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B45" s="7" t="s">
-        <v>1206</v>
+        <v>1203</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B46" s="7" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="2:9" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B47" s="7" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B48" s="7" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="D48" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>1045</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>1036</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B49" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>1266</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B50" s="7" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>1258</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B51" s="7" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="52" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B52" s="7" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="53" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B53" s="7" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1259</v>
+        <v>1256</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B54" s="7" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="C54" s="7" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D54" s="7" t="s">
         <v>1249</v>
       </c>
-      <c r="D54" s="7" t="s">
-        <v>1252</v>
-      </c>
       <c r="E54" s="7" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B55" s="7" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1221</v>
+        <v>1218</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="57" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B57" s="7" t="s">
-        <v>1224</v>
+        <v>1221</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>1261</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="7" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>1260</v>
+        <v>1257</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="59" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B59" s="7" t="s">
-        <v>1227</v>
+        <v>1224</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="60" spans="2:6" ht="32.4" x14ac:dyDescent="0.3">
       <c r="B60" s="7" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1265</v>
+        <v>1262</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1267</v>
+        <v>1264</v>
       </c>
     </row>
   </sheetData>
@@ -15195,7 +15313,7 @@
         <v>613</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>47</v>
@@ -15215,13 +15333,13 @@
         <v>84</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>91</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -15232,10 +15350,10 @@
         <v>615</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>48</v>
@@ -15258,7 +15376,7 @@
         <v>87</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>600</v>
@@ -15289,19 +15407,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>1319</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>1323</v>
-      </c>
       <c r="D18" s="7" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32.4" x14ac:dyDescent="0.3">
@@ -15315,7 +15433,7 @@
         <v>55</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>70</v>
@@ -15998,7 +16116,7 @@
         <v>100</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>372</v>
@@ -16132,7 +16250,7 @@
         <v>674</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>675</v>

--- a/expData.xlsx
+++ b/expData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5070338-37D0-4E44-9BB1-384AED8815B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65636627-0427-4306-9F9F-B423E6AC0ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="1520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="1522">
   <si>
     <t>activeScence</t>
   </si>
@@ -3593,9 +3593,6 @@
     <t>Terrace</t>
   </si>
   <si>
-    <t>Porch</t>
-  </si>
-  <si>
     <t>Courtyard</t>
   </si>
   <si>
@@ -4357,10 +4354,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>paradise</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Estate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4994,6 +4987,22 @@
   </si>
   <si>
     <t>Orchard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auditorium</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cliff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cliff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Porch</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5442,7 +5451,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5498,7 +5507,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="E5" s="4" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +5600,7 @@
         <v>145</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>153</v>
@@ -5631,7 +5640,7 @@
         <v>145</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>126</v>
@@ -5657,7 +5666,7 @@
         <v>151</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5731,7 +5740,7 @@
         <v>114</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>132</v>
@@ -5748,7 +5757,7 @@
         <v>705</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>120</v>
@@ -5868,7 +5877,7 @@
         <v>711</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>149</v>
@@ -5888,7 +5897,7 @@
         <v>700</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>131</v>
@@ -5912,10 +5921,10 @@
         <v>149</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>147</v>
@@ -6035,7 +6044,7 @@
         <v>678</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>405</v>
@@ -6062,7 +6071,7 @@
         <v>671</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>437</v>
@@ -6076,13 +6085,13 @@
         <v>681</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>417</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>64</v>
@@ -6133,7 +6142,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>675</v>
@@ -6142,7 +6151,7 @@
         <v>449</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>403</v>
@@ -6199,7 +6208,7 @@
         <v>671</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>425</v>
@@ -6216,7 +6225,7 @@
         <v>687</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>421</v>
@@ -6239,10 +6248,10 @@
         <v>452</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>411</v>
@@ -6379,7 +6388,7 @@
         <v>130</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>421</v>
@@ -6696,7 +6705,7 @@
         <v>731</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>671</v>
@@ -6784,7 +6793,7 @@
         <v>279</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="32.4">
@@ -6792,19 +6801,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="C2" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="32.4">
@@ -6812,19 +6821,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>1406</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>1410</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>1409</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>1408</v>
-      </c>
       <c r="F3" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -6832,19 +6841,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>1411</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>1415</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1414</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1413</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="32.4">
@@ -6852,19 +6861,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -6872,16 +6881,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>1417</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>1405</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>1419</v>
-      </c>
       <c r="E6" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>522</v>
@@ -6892,19 +6901,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>1420</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>1423</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1408</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>1422</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="32.4">
@@ -6912,19 +6921,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>1424</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>1426</v>
-      </c>
       <c r="D8" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="32.4">
@@ -6932,19 +6941,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>1427</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>1431</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>1430</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>1429</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="G9" s="7"/>
     </row>
@@ -6953,19 +6962,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>1408</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>1410</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>1412</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -6974,13 +6983,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>524</v>
@@ -6995,19 +7004,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="G12" s="7"/>
     </row>
@@ -7016,19 +7025,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>522</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="G13" s="7"/>
     </row>
@@ -7037,19 +7046,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>572</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="G14" s="7"/>
     </row>
@@ -7058,19 +7067,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>1443</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>1330</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>1445</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>576</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="G15" s="7"/>
     </row>
@@ -7079,19 +7088,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>575</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>555</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="G16" s="7"/>
     </row>
@@ -7100,19 +7109,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="G17" s="7"/>
     </row>
@@ -7121,19 +7130,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>273</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7141,16 +7150,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>558</v>
@@ -7161,19 +7170,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>576</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>575</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -7181,19 +7190,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>1438</v>
       </c>
-      <c r="C21" s="9" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>1440</v>
-      </c>
       <c r="E21" s="9" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -7204,16 +7213,16 @@
         <v>734</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>512</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7224,7 +7233,7 @@
         <v>735</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>483</v>
@@ -7241,7 +7250,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>503</v>
@@ -7281,7 +7290,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>272</v>
@@ -7290,7 +7299,7 @@
         <v>524</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>470</v>
@@ -7341,7 +7350,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>483</v>
@@ -7564,7 +7573,7 @@
         <v>750</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>512</v>
@@ -7585,7 +7594,7 @@
         <v>751</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>508</v>
@@ -7606,7 +7615,7 @@
         <v>752</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>483</v>
@@ -7732,7 +7741,7 @@
         <v>762</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>506</v>
@@ -7774,7 +7783,7 @@
         <v>766</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>483</v>
@@ -7861,13 +7870,13 @@
         <v>773</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="G54" s="7"/>
     </row>
@@ -7879,7 +7888,7 @@
         <v>774</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>501</v>
@@ -7888,7 +7897,7 @@
         <v>516</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="G55" s="7"/>
     </row>
@@ -7923,13 +7932,13 @@
         <v>512</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>501</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -7940,7 +7949,7 @@
         <v>777</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>506</v>
@@ -8158,7 +8167,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -8167,7 +8176,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8184,7 +8193,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -8198,7 +8207,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -8363,7 +8372,7 @@
         <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8888,7 +8897,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>206</v>
@@ -8965,7 +8974,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>343</v>
@@ -9042,10 +9051,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -9130,10 +9139,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -9163,7 +9172,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>357</v>
@@ -9174,10 +9183,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -9207,10 +9216,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -9240,7 +9249,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>363</v>
@@ -9375,7 +9384,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>115</v>
@@ -9419,7 +9428,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>123</v>
@@ -9463,10 +9472,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>1341</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -9474,10 +9483,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>1343</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9485,7 +9494,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>133</v>
@@ -9518,7 +9527,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>138</v>
@@ -9540,7 +9549,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>141</v>
@@ -9551,7 +9560,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>142</v>
@@ -9705,7 +9714,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>436</v>
@@ -9716,7 +9725,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>438</v>
@@ -9771,7 +9780,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>158</v>
@@ -9782,7 +9791,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>407</v>
@@ -9936,7 +9945,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>449</v>
+        <v>1519</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>450</v>
@@ -10013,7 +10022,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>284</v>
+        <v>1518</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>285</v>
@@ -10057,7 +10066,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>293</v>
@@ -10093,7 +10102,7 @@
         <v>298</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -10266,7 +10275,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>330</v>
@@ -10299,7 +10308,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>334</v>
@@ -10332,7 +10341,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>339</v>
@@ -10379,10 +10388,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -10445,10 +10454,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>1288</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10478,10 +10487,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>1305</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -10503,7 +10512,7 @@
         <v>476</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -10591,7 +10600,7 @@
         <v>574</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -10602,7 +10611,7 @@
         <v>492</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -10657,7 +10666,7 @@
         <v>524</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -10668,7 +10677,7 @@
         <v>503</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -10734,7 +10743,7 @@
         <v>558</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -10745,7 +10754,7 @@
         <v>557</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -10775,10 +10784,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C38" s="11" t="s">
         <v>1286</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -10808,10 +10817,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>1309</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -10830,10 +10839,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -10874,10 +10883,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>1333</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -10888,7 +10897,7 @@
         <v>575</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -10918,10 +10927,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>1330</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -10962,10 +10971,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>1317</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -11050,10 +11059,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -11083,10 +11092,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>1314</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -11105,10 +11114,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>1335</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -11116,10 +11125,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>1319</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -11127,10 +11136,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -11149,10 +11158,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -11174,7 +11183,7 @@
         <v>586</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -11237,7 +11246,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C80" t="s">
         <v>220</v>
@@ -11303,7 +11312,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="C86" t="s">
         <v>232</v>
@@ -11416,7 +11425,7 @@
         <v>246</v>
       </c>
       <c r="C96" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -11446,10 +11455,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C99" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -11457,10 +11466,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="C100" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -11468,7 +11477,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C101" t="s">
         <v>252</v>
@@ -11490,7 +11499,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C103" t="s">
         <v>255</v>
@@ -11523,10 +11532,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C106" t="s">
         <v>1323</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -11545,7 +11554,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="C108" t="s">
         <v>261</v>
@@ -11559,7 +11568,7 @@
         <v>455</v>
       </c>
       <c r="C109" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -11570,7 +11579,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -11581,7 +11590,7 @@
         <v>263</v>
       </c>
       <c r="C111" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -11759,13 +11768,13 @@
         <v>814</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>815</v>
@@ -11798,7 +11807,7 @@
         <v>793</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>815</v>
@@ -11813,7 +11822,7 @@
         <v>822</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>823</v>
@@ -11831,13 +11840,13 @@
         <v>825</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>802</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>803</v>
@@ -11855,7 +11864,7 @@
         <v>792</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>793</v>
@@ -11885,7 +11894,7 @@
         <v>830</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>792</v>
@@ -11906,7 +11915,7 @@
         <v>832</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>834</v>
@@ -11930,7 +11939,7 @@
         <v>829</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="H16" s="3"/>
     </row>
@@ -11939,7 +11948,7 @@
         <v>838</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>793</v>
@@ -11992,10 +12001,10 @@
         <v>844</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>815</v>
@@ -12018,7 +12027,7 @@
         <v>818</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="32.4">
@@ -12094,7 +12103,7 @@
         <v>863</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>856</v>
@@ -12182,10 +12191,10 @@
         <v>878</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>879</v>
@@ -12202,7 +12211,7 @@
         <v>874</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>881</v>
@@ -12247,7 +12256,7 @@
         <v>888</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>856</v>
@@ -12338,7 +12347,7 @@
         <v>874</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>872</v>
@@ -12363,7 +12372,7 @@
     </row>
     <row r="42" spans="2:8" ht="32.4">
       <c r="B42" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>910</v>
@@ -12372,24 +12381,24 @@
         <v>796</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="32.4">
       <c r="B43" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>847</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>788</v>
@@ -12397,13 +12406,13 @@
     </row>
     <row r="44" spans="2:8" ht="32.4">
       <c r="B44" s="7" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>916</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>917</v>
@@ -12414,16 +12423,16 @@
     </row>
     <row r="45" spans="2:8" ht="32.4">
       <c r="B45" s="7" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>1251</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>1252</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>924</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>910</v>
@@ -12431,10 +12440,10 @@
     </row>
     <row r="46" spans="2:8" ht="32.4">
       <c r="B46" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>927</v>
@@ -12448,13 +12457,13 @@
     </row>
     <row r="47" spans="2:8" ht="32.4">
       <c r="B47" s="7" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>1255</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>1256</v>
-      </c>
       <c r="D47" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>911</v>
@@ -12467,16 +12476,16 @@
     </row>
     <row r="48" spans="2:8" ht="32.4">
       <c r="B48" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>913</v>
@@ -12486,7 +12495,7 @@
     </row>
     <row r="49" spans="2:8" ht="32.4">
       <c r="B49" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>919</v>
@@ -12495,7 +12504,7 @@
         <v>915</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>914</v>
@@ -12505,13 +12514,13 @@
     </row>
     <row r="50" spans="2:8" ht="32.4">
       <c r="B50" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>920</v>
@@ -12524,13 +12533,13 @@
     </row>
     <row r="51" spans="2:8" ht="32.4">
       <c r="B51" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>919</v>
@@ -12543,10 +12552,10 @@
     </row>
     <row r="52" spans="2:8" ht="32.4">
       <c r="B52" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>913</v>
@@ -12555,23 +12564,23 @@
         <v>926</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
     </row>
     <row r="53" spans="2:8" ht="32.4">
       <c r="B53" s="7" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>917</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>919</v>
@@ -12581,7 +12590,7 @@
     </row>
     <row r="54" spans="2:8" ht="32.4">
       <c r="B54" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>918</v>
@@ -12590,7 +12599,7 @@
         <v>925</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>916</v>
@@ -12600,7 +12609,7 @@
     </row>
     <row r="55" spans="2:8" ht="32.4">
       <c r="B55" s="7" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>925</v>
@@ -12619,45 +12628,45 @@
     </row>
     <row r="56" spans="2:8" ht="32.4">
       <c r="B56" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>867</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>832</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
     </row>
     <row r="57" spans="2:8" ht="32.4">
       <c r="B57" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>919</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>917</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
     </row>
     <row r="58" spans="2:8" ht="32.4">
       <c r="B58" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>926</v>
@@ -12669,20 +12678,20 @@
         <v>832</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
     </row>
     <row r="59" spans="2:8" ht="32.4">
       <c r="B59" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>910</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>923</v>
@@ -12695,19 +12704,19 @@
     </row>
     <row r="60" spans="2:8" ht="32.4">
       <c r="B60" s="7" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -12829,7 +12838,7 @@
         <v>1044</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -12846,7 +12855,7 @@
         <v>797</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>1048</v>
@@ -12863,10 +12872,10 @@
         <v>1050</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>1511</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1513</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>1052</v>
@@ -12880,13 +12889,13 @@
         <v>1053</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>1055</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>1056</v>
+      <c r="E5" s="8" t="s">
+        <v>1354</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>1057</v>
@@ -12904,13 +12913,13 @@
         <v>1059</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>1060</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -12921,14 +12930,14 @@
       <c r="B7" s="7" t="s">
         <v>1061</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>1355</v>
+      <c r="C7" s="12" t="s">
+        <v>1509</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>1043</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>1062</v>
@@ -12943,7 +12952,7 @@
         <v>1063</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>1064</v>
@@ -12966,13 +12975,13 @@
         <v>1043</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>907</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="32.4">
@@ -13003,13 +13012,13 @@
         <v>1069</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>1070</v>
@@ -13026,13 +13035,13 @@
         <v>1042</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="32.4">
@@ -13046,7 +13055,7 @@
         <v>907</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>1074</v>
@@ -13063,10 +13072,10 @@
         <v>1076</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1516</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>1355</v>
+        <v>1514</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>1354</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>1077</v>
@@ -13086,10 +13095,10 @@
         <v>1048</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>1047</v>
@@ -13106,10 +13115,10 @@
         <v>1042</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>1059</v>
@@ -13123,10 +13132,10 @@
         <v>1080</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>1054</v>
@@ -13149,10 +13158,10 @@
         <v>1044</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -13163,7 +13172,7 @@
         <v>1084</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>1054</v>
@@ -13186,10 +13195,10 @@
         <v>1073</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>1088</v>
@@ -13203,16 +13212,16 @@
         <v>1089</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>1054</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="32.4">
@@ -13246,7 +13255,7 @@
         <v>1044</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>1042</v>
@@ -13286,7 +13295,7 @@
         <v>1054</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>1055</v>
@@ -13303,7 +13312,7 @@
         <v>1104</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>1059</v>
@@ -13343,13 +13352,13 @@
         <v>1107</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>1054</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>797</v>
@@ -13362,7 +13371,7 @@
       <c r="B29" s="7" t="s">
         <v>1108</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>1056</v>
       </c>
       <c r="D29" s="7" t="s">
@@ -13383,7 +13392,7 @@
         <v>1109</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>1059</v>
@@ -13409,7 +13418,7 @@
         <v>1042</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>1111</v>
@@ -13423,13 +13432,13 @@
         <v>1112</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>1044</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>1081</v>
@@ -13443,13 +13452,13 @@
         <v>1113</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>1042</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>1355</v>
+      <c r="E33" s="8" t="s">
+        <v>1354</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>1114</v>
@@ -13464,7 +13473,7 @@
         <v>1115</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>1106</v>
@@ -13473,7 +13482,7 @@
         <v>1054</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="32.4">
@@ -13508,10 +13517,10 @@
         <v>1042</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>910</v>
@@ -13528,10 +13537,10 @@
         <v>1048</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>1120</v>
@@ -13574,7 +13583,7 @@
         <v>1055</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="32.4">
@@ -13585,13 +13594,13 @@
         <v>1124</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>1056</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>796</v>
@@ -13625,13 +13634,13 @@
         <v>1129</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>1376</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>1056</v>
+        <v>1374</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>1520</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>1130</v>
@@ -13645,7 +13654,7 @@
         <v>1131</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>907</v>
@@ -13662,19 +13671,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>1133</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>1134</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="G44" s="3"/>
     </row>
@@ -13689,7 +13698,7 @@
         <v>1042</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>1091</v>
@@ -13707,13 +13716,13 @@
         <v>1137</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>1087</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>1138</v>
@@ -13734,7 +13743,7 @@
         <v>1051</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>1141</v>
@@ -13776,10 +13785,10 @@
         <v>1147</v>
       </c>
       <c r="E49" s="7" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>1148</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>1149</v>
       </c>
       <c r="G49" s="3"/>
     </row>
@@ -13788,10 +13797,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>1044</v>
@@ -13800,7 +13809,7 @@
         <v>1059</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -13810,7 +13819,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>1083</v>
@@ -13819,7 +13828,7 @@
         <v>1092</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>923</v>
@@ -13831,19 +13840,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>1042</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>1055</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="H52" s="3"/>
     </row>
@@ -13852,19 +13861,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>907</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="H53" s="3"/>
     </row>
@@ -13873,7 +13882,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>1116</v>
@@ -13882,10 +13891,10 @@
         <v>1094</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H54" s="3"/>
     </row>
@@ -13894,19 +13903,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D55" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>1159</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="F55" s="7" t="s">
         <v>1160</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>1161</v>
       </c>
       <c r="H55" s="3"/>
     </row>
@@ -13915,7 +13924,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>1093</v>
@@ -13927,7 +13936,7 @@
         <v>1046</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H56" s="3"/>
     </row>
@@ -13936,7 +13945,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>1050</v>
@@ -13945,10 +13954,10 @@
         <v>1062</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="H57" s="3"/>
     </row>
@@ -13957,19 +13966,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>1116</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>1056</v>
+      <c r="D58" s="12" t="s">
+        <v>1521</v>
       </c>
       <c r="E58" s="7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F58" s="7" t="s">
         <v>1167</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>1168</v>
       </c>
       <c r="H58" s="3"/>
     </row>
@@ -13978,19 +13987,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="D59" s="7" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>1170</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>1360</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="32.4">
@@ -13998,19 +14007,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="D60" s="7" t="s">
         <v>1173</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="E60" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="F60" s="7" t="s">
         <v>1175</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="32.4">
@@ -14018,19 +14027,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>1177</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>1519</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>1377</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>1383</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>1178</v>
       </c>
     </row>
   </sheetData>
@@ -14267,7 +14276,7 @@
         <v>962</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>958</v>
@@ -14284,7 +14293,7 @@
         <v>964</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>921</v>
@@ -14318,7 +14327,7 @@
         <v>959</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>952</v>
@@ -14369,7 +14378,7 @@
         <v>945</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>964</v>
@@ -14454,7 +14463,7 @@
         <v>964</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>974</v>
@@ -14525,7 +14534,7 @@
         <v>948</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>1003</v>
@@ -14570,7 +14579,7 @@
         <v>1007</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>1008</v>
@@ -14587,16 +14596,16 @@
         <v>1010</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>975</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="32.4">
@@ -14610,7 +14619,7 @@
         <v>936</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>945</v>
@@ -14622,16 +14631,16 @@
         <v>1012</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>1210</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>1211</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>936</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="H34" s="7"/>
     </row>
@@ -14640,10 +14649,10 @@
         <v>1013</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>964</v>
@@ -14695,10 +14704,10 @@
         <v>1020</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>1022</v>
@@ -14731,16 +14740,16 @@
         <v>1026</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>945</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="I40" s="7"/>
     </row>
@@ -14764,28 +14773,28 @@
     </row>
     <row r="42" spans="2:9" ht="32.4">
       <c r="B42" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>1179</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="D42" s="7" t="s">
         <v>1180</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>1181</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>952</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="2:9" ht="32.4">
       <c r="B43" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>1182</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>1183</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>952</v>
@@ -14794,31 +14803,31 @@
         <v>998</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="2:9" ht="32.4">
       <c r="B44" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>942</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="2:9" ht="32.4">
       <c r="B45" s="7" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>1039</v>
@@ -14836,7 +14845,7 @@
     </row>
     <row r="46" spans="2:9" ht="32.4">
       <c r="B46" s="7" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>1022</v>
@@ -14854,28 +14863,28 @@
     </row>
     <row r="47" spans="2:9" ht="32.4">
       <c r="B47" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>1188</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>1189</v>
-      </c>
       <c r="D47" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>957</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>1190</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>1191</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>1030</v>
@@ -14889,7 +14898,7 @@
     </row>
     <row r="49" spans="2:6" ht="32.4">
       <c r="B49" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>942</v>
@@ -14901,38 +14910,38 @@
         <v>1031</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="32.4">
       <c r="B50" s="7" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>952</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="32.4">
       <c r="B51" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>1194</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D51" s="7" t="s">
+      <c r="E51" s="7" t="s">
         <v>1195</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>1196</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>1034</v>
@@ -14940,13 +14949,13 @@
     </row>
     <row r="52" spans="2:6" ht="32.4">
       <c r="B52" s="7" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>961</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>1000</v>
@@ -14957,13 +14966,13 @@
     </row>
     <row r="53" spans="2:6" ht="32.4">
       <c r="B53" s="7" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>1036</v>
@@ -14974,84 +14983,84 @@
     </row>
     <row r="54" spans="2:6" ht="32.4">
       <c r="B54" s="7" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>1030</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="32.4">
       <c r="B55" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>1200</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>1228</v>
-      </c>
-      <c r="D55" s="7" t="s">
+      <c r="E55" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>1202</v>
-      </c>
       <c r="F55" s="7" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="7" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>1029</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>966</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="57" spans="2:6" ht="32.4">
       <c r="B57" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>1204</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="F57" s="7" t="s">
         <v>1240</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>1205</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="7" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>1039</v>
@@ -15059,13 +15068,13 @@
     </row>
     <row r="59" spans="2:6" ht="32.4">
       <c r="B59" s="7" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>942</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>1038</v>
@@ -15076,19 +15085,19 @@
     </row>
     <row r="60" spans="2:6" ht="32.4">
       <c r="B60" s="7" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
   </sheetData>
@@ -15360,7 +15369,7 @@
         <v>602</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>47</v>
@@ -15380,13 +15389,13 @@
         <v>84</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>91</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15397,10 +15406,10 @@
         <v>604</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>48</v>
@@ -15423,7 +15432,7 @@
         <v>87</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>589</v>
@@ -15454,19 +15463,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32.4">
@@ -15480,7 +15489,7 @@
         <v>55</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>70</v>
@@ -16163,7 +16172,7 @@
         <v>100</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>364</v>
@@ -16297,7 +16306,7 @@
         <v>663</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>664</v>

--- a/expData.xlsx
+++ b/expData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65636627-0427-4306-9F9F-B423E6AC0ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08099525-40CD-4450-A16A-5608CE4CD963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="1522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="1526">
   <si>
     <t>activeScence</t>
   </si>
@@ -1956,9 +1956,6 @@
     <t>The teacher asked a difficult _______ about the topic of evolution.</t>
   </si>
   <si>
-    <t>Jane opened her _______ to take notes during the lecture.</t>
-  </si>
-  <si>
     <t>textbook</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5003,6 +5000,26 @@
   </si>
   <si>
     <t>Porch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jane opened her _______ to take notes during the lecture.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notebook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ruler</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Angry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Serious</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5451,7 +5468,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5462,7 +5479,7 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -5496,7 +5513,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -5507,7 +5524,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="E5" s="4" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
   </sheetData>
@@ -5554,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>130</v>
@@ -5574,7 +5591,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>114</v>
@@ -5594,13 +5611,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>145</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>153</v>
@@ -5614,13 +5631,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>124</v>
@@ -5634,13 +5651,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>145</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>126</v>
@@ -5654,19 +5671,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>157</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>151</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5674,7 +5691,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>124</v>
@@ -5694,7 +5711,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>151</v>
@@ -5703,7 +5720,7 @@
         <v>114</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>131</v>
@@ -5714,7 +5731,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>147</v>
@@ -5734,13 +5751,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>114</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>132</v>
@@ -5754,10 +5771,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>120</v>
@@ -5774,7 +5791,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>149</v>
@@ -5794,7 +5811,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>134</v>
@@ -5814,16 +5831,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>695</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>696</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>157</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>108</v>
@@ -5834,7 +5851,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>145</v>
@@ -5854,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>134</v>
@@ -5874,10 +5891,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>149</v>
@@ -5894,10 +5911,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>131</v>
@@ -5915,16 +5932,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>149</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>1386</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>1387</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>147</v>
@@ -5936,7 +5953,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>134</v>
@@ -5957,7 +5974,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>411</v>
@@ -5966,7 +5983,7 @@
         <v>431</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>442</v>
@@ -5978,7 +5995,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>429</v>
@@ -5987,7 +6004,7 @@
         <v>425</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>444</v>
@@ -5999,13 +6016,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>419</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>411</v>
@@ -6020,7 +6037,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>402</v>
@@ -6029,7 +6046,7 @@
         <v>449</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>446</v>
@@ -6041,10 +6058,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>405</v>
@@ -6062,16 +6079,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="C27" s="7" t="s">
-        <v>680</v>
-      </c>
       <c r="D27" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>437</v>
@@ -6082,16 +6099,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>417</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>64</v>
@@ -6102,7 +6119,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>442</v>
@@ -6122,7 +6139,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>429</v>
@@ -6142,16 +6159,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>449</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>403</v>
@@ -6162,10 +6179,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>451</v>
@@ -6174,7 +6191,7 @@
         <v>405</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -6182,7 +6199,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>417</v>
@@ -6202,13 +6219,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>425</v>
@@ -6222,16 +6239,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>421</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>408</v>
@@ -6242,16 +6259,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>452</v>
       </c>
       <c r="D36" s="7" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E36" s="7" t="s">
         <v>1394</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>1395</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>411</v>
@@ -6262,7 +6279,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>405</v>
@@ -6282,7 +6299,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>419</v>
@@ -6294,7 +6311,7 @@
         <v>421</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -6302,7 +6319,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>411</v>
@@ -6322,7 +6339,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>429</v>
@@ -6331,7 +6348,7 @@
         <v>452</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>421</v>
@@ -6342,7 +6359,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>452</v>
@@ -6354,7 +6371,7 @@
         <v>449</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="32.4">
@@ -6362,7 +6379,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>296</v>
@@ -6382,13 +6399,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>130</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>421</v>
@@ -6402,7 +6419,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>332</v>
@@ -6422,7 +6439,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>299</v>
@@ -6442,7 +6459,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>331</v>
@@ -6462,7 +6479,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>338</v>
@@ -6482,7 +6499,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>282</v>
@@ -6502,7 +6519,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>299</v>
@@ -6522,7 +6539,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>329</v>
@@ -6531,7 +6548,7 @@
         <v>336</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>298</v>
@@ -6542,7 +6559,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>332</v>
@@ -6562,7 +6579,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>305</v>
@@ -6582,10 +6599,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>288</v>
@@ -6602,7 +6619,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>282</v>
@@ -6622,7 +6639,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>130</v>
@@ -6642,7 +6659,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>64</v>
@@ -6662,7 +6679,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>290</v>
@@ -6682,7 +6699,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>299</v>
@@ -6702,13 +6719,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>329</v>
@@ -6722,7 +6739,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>421</v>
@@ -6742,7 +6759,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>335</v>
@@ -6793,7 +6810,7 @@
         <v>279</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="32.4">
@@ -6801,19 +6818,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C2" t="s">
         <v>1401</v>
       </c>
-      <c r="C2" t="s">
-        <v>1402</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="32.4">
@@ -6821,19 +6838,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>1404</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>1408</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>1407</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>1406</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -6841,19 +6858,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>1409</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1412</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1411</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="32.4">
@@ -6861,19 +6878,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -6881,16 +6898,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>1415</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>1416</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>522</v>
@@ -6901,19 +6918,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>1418</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1421</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1406</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>1420</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>1419</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="32.4">
@@ -6921,19 +6938,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>1422</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>1424</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>1304</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>1402</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="32.4">
@@ -6941,19 +6958,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>1425</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>1428</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>1427</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>1426</v>
       </c>
       <c r="G9" s="7"/>
     </row>
@@ -6962,19 +6979,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -6983,13 +7000,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>524</v>
@@ -7004,19 +7021,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>1432</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>1285</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>1433</v>
-      </c>
       <c r="F12" s="7" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="G12" s="7"/>
     </row>
@@ -7025,19 +7042,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>522</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="G13" s="7"/>
     </row>
@@ -7046,19 +7063,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>572</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="G14" s="7"/>
     </row>
@@ -7067,19 +7084,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>576</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="G15" s="7"/>
     </row>
@@ -7088,19 +7105,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>575</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>555</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="G16" s="7"/>
     </row>
@@ -7109,19 +7126,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="7"/>
     </row>
@@ -7130,19 +7147,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>273</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7150,16 +7167,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>1451</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>1429</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>1304</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>1452</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>558</v>
@@ -7170,19 +7187,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>576</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>575</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -7190,19 +7207,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>1436</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="D21" s="9" t="s">
         <v>1437</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>1438</v>
-      </c>
       <c r="E21" s="9" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -7210,19 +7227,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>512</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7230,10 +7247,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>483</v>
@@ -7250,7 +7267,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>503</v>
@@ -7262,7 +7279,7 @@
         <v>518</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -7270,7 +7287,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>483</v>
@@ -7290,7 +7307,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>272</v>
@@ -7299,7 +7316,7 @@
         <v>524</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>470</v>
@@ -7310,7 +7327,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>520</v>
@@ -7330,7 +7347,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>516</v>
@@ -7350,7 +7367,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>483</v>
@@ -7370,7 +7387,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>555</v>
@@ -7390,7 +7407,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>465</v>
@@ -7410,7 +7427,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>463</v>
@@ -7430,7 +7447,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>469</v>
@@ -7450,7 +7467,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>514</v>
@@ -7470,7 +7487,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>470</v>
@@ -7490,7 +7507,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>514</v>
@@ -7510,7 +7527,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>520</v>
@@ -7530,7 +7547,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>512</v>
@@ -7550,7 +7567,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>514</v>
@@ -7570,10 +7587,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>512</v>
@@ -7591,10 +7608,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>508</v>
@@ -7612,10 +7629,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>483</v>
@@ -7633,16 +7650,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>753</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>754</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>539</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>553</v>
@@ -7654,7 +7671,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>459</v>
@@ -7675,10 +7692,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>757</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>758</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>549</v>
@@ -7696,13 +7713,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>536</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>251</v>
@@ -7717,7 +7734,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>530</v>
@@ -7738,10 +7755,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>506</v>
@@ -7759,19 +7776,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>251</v>
       </c>
       <c r="D49" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>765</v>
-      </c>
       <c r="F49" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G49" s="7"/>
     </row>
@@ -7780,10 +7797,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>483</v>
@@ -7801,7 +7818,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>512</v>
@@ -7822,13 +7839,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>549</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>543</v>
@@ -7843,13 +7860,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="C53" s="7" t="s">
         <v>769</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="D53" s="7" t="s">
         <v>770</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>771</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>531</v>
@@ -7864,19 +7881,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="C54" s="7" t="s">
         <v>772</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>773</v>
-      </c>
       <c r="D54" s="7" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>1461</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>1462</v>
-      </c>
       <c r="F54" s="7" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="G54" s="7"/>
     </row>
@@ -7885,10 +7902,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>501</v>
@@ -7897,7 +7914,7 @@
         <v>516</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="G55" s="7"/>
     </row>
@@ -7906,7 +7923,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>530</v>
@@ -7926,19 +7943,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>512</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>501</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -7946,16 +7963,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>506</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>534</v>
@@ -7966,10 +7983,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>779</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>780</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>512</v>
@@ -7978,7 +7995,7 @@
         <v>530</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="32.4">
@@ -7986,7 +8003,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>459</v>
@@ -8006,7 +8023,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>556</v>
@@ -8015,7 +8032,7 @@
         <v>501</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>530</v>
@@ -8167,7 +8184,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -8176,7 +8193,7 @@
         <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8193,7 +8210,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -8207,7 +8224,7 @@
         <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -8372,7 +8389,7 @@
         <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8897,7 +8914,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>206</v>
@@ -8974,7 +8991,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>343</v>
@@ -9051,10 +9068,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>1495</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -9139,10 +9156,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C78" s="7" t="s">
         <v>1487</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -9172,7 +9189,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>357</v>
@@ -9183,10 +9200,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>1481</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -9216,10 +9233,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C85" s="7" t="s">
         <v>1483</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>1484</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -9249,7 +9266,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>363</v>
@@ -9362,7 +9379,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>111</v>
@@ -9384,7 +9401,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>115</v>
@@ -9428,7 +9445,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>123</v>
@@ -9472,10 +9489,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>1340</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -9483,10 +9500,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>1342</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9494,7 +9511,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>133</v>
@@ -9527,7 +9544,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>138</v>
@@ -9549,7 +9566,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>141</v>
@@ -9560,7 +9577,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>142</v>
@@ -9714,7 +9731,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>436</v>
@@ -9725,7 +9742,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>438</v>
@@ -9780,7 +9797,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>158</v>
@@ -9791,7 +9808,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>407</v>
@@ -9945,7 +9962,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>450</v>
@@ -9967,7 +9984,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>439</v>
@@ -9989,7 +10006,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>454</v>
@@ -10022,7 +10039,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>285</v>
@@ -10066,7 +10083,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>293</v>
@@ -10102,7 +10119,7 @@
         <v>298</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -10275,7 +10292,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>330</v>
@@ -10308,7 +10325,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>334</v>
@@ -10341,7 +10358,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>339</v>
@@ -10388,10 +10405,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -10454,10 +10471,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>1287</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10487,10 +10504,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>1304</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -10512,7 +10529,7 @@
         <v>476</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -10600,7 +10617,7 @@
         <v>574</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -10611,7 +10628,7 @@
         <v>492</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -10666,7 +10683,7 @@
         <v>524</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -10677,7 +10694,7 @@
         <v>503</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -10743,7 +10760,7 @@
         <v>558</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -10754,7 +10771,7 @@
         <v>557</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -10784,10 +10801,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="11" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C38" s="11" t="s">
         <v>1285</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -10817,10 +10834,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C41" s="7" t="s">
         <v>1308</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -10839,10 +10856,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>1464</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -10883,10 +10900,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>1332</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -10897,7 +10914,7 @@
         <v>575</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -10927,10 +10944,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>1329</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -10971,10 +10988,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>1316</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -11059,10 +11076,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="12" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C63" s="7" t="s">
         <v>1493</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -11092,10 +11109,10 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C66" s="7" t="s">
         <v>1313</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -11114,10 +11131,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>1334</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -11125,10 +11142,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C69" s="7" t="s">
         <v>1318</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -11136,10 +11153,10 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C70" s="7" t="s">
         <v>1497</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -11158,10 +11175,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="11" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>1491</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -11183,7 +11200,7 @@
         <v>586</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -11246,7 +11263,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C80" t="s">
         <v>220</v>
@@ -11312,7 +11329,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="C86" t="s">
         <v>232</v>
@@ -11425,7 +11442,7 @@
         <v>246</v>
       </c>
       <c r="C96" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="97" spans="1:3">
@@ -11455,10 +11472,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C99" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -11466,10 +11483,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C100" t="s">
         <v>1499</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -11477,7 +11494,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C101" t="s">
         <v>252</v>
@@ -11499,7 +11516,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C103" t="s">
         <v>255</v>
@@ -11532,10 +11549,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C106" t="s">
         <v>1322</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="107" spans="1:3">
@@ -11554,7 +11571,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C108" t="s">
         <v>261</v>
@@ -11568,7 +11585,7 @@
         <v>455</v>
       </c>
       <c r="C109" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="110" spans="1:3">
@@ -11579,7 +11596,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="111" spans="1:3">
@@ -11590,7 +11607,7 @@
         <v>263</v>
       </c>
       <c r="C111" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="112" spans="1:3">
@@ -11676,159 +11693,159 @@
     </row>
     <row r="2" spans="1:8" ht="32.4">
       <c r="B2" s="7" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>40</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>792</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>793</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="32.4">
       <c r="B3" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>795</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>796</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>797</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>798</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>799</v>
       </c>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="32.4">
       <c r="B4" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>800</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>801</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>802</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>803</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>804</v>
       </c>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="32.4">
       <c r="B5" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>805</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>806</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>808</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>809</v>
       </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8">
       <c r="B6" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>811</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>812</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>813</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8">
       <c r="B7" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>814</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>1466</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1472</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>1466</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>815</v>
       </c>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8">
       <c r="B8" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>816</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>818</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>819</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>820</v>
       </c>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8">
       <c r="B10" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>822</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>1468</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>823</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>824</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>80</v>
@@ -11837,70 +11854,70 @@
     </row>
     <row r="11" spans="1:8" ht="32.4">
       <c r="B11" s="7" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>802</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>1472</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>803</v>
       </c>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" ht="32.4">
       <c r="B12" s="7" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>792</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>1501</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>793</v>
       </c>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>828</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>817</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>813</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>829</v>
-      </c>
       <c r="F13" s="7" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8" ht="32.4">
       <c r="B14" s="7" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>40</v>
@@ -11909,105 +11926,105 @@
     </row>
     <row r="15" spans="1:8" ht="32.4">
       <c r="B15" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>831</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>832</v>
-      </c>
       <c r="D15" s="7" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="E15" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>834</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>835</v>
       </c>
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="1:8" ht="32.4">
       <c r="B16" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>836</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>837</v>
-      </c>
       <c r="D16" s="7" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="2:8" ht="32.4">
       <c r="B17" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>838</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>1467</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>793</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>815</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>839</v>
       </c>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="2:8" ht="32.4">
       <c r="B18" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>840</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="D18" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>841</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>833</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>842</v>
       </c>
       <c r="H18" s="3"/>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" s="7" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" s="7" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>40</v>
@@ -12015,708 +12032,708 @@
     </row>
     <row r="21" spans="2:8" s="10" customFormat="1">
       <c r="B21" s="8" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>816</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>817</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>818</v>
-      </c>
       <c r="F21" s="8" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="32.4">
       <c r="B22" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>846</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="7" t="s">
         <v>847</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="7" t="s">
         <v>848</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>849</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="7" t="s">
+        <v>850</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>851</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>806</v>
-      </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>852</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>853</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="32.4">
       <c r="B24" s="7" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D24" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>855</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>856</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="32.4">
       <c r="B25" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>858</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="D25" s="7" t="s">
         <v>859</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>860</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>861</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>863</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>1473</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>856</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>826</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="7" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="32.4">
       <c r="B28" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>866</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="D28" s="7" t="s">
         <v>867</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="E28" s="7" t="s">
         <v>868</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="F28" s="7" t="s">
         <v>869</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="32.4">
       <c r="B29" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>871</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="7" t="s">
         <v>872</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="E29" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>873</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>854</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="32.4">
       <c r="B30" s="7" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>875</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>859</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>860</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="32.4">
       <c r="B31" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>877</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>878</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>1473</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>1474</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="32" spans="2:8" ht="32.4">
       <c r="B32" s="7" t="s">
+        <v>879</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>880</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>856</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>874</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>1475</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="7" t="s">
+        <v>881</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>882</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>883</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="E33" s="7" t="s">
         <v>884</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>885</v>
-      </c>
       <c r="F33" s="7" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" s="7" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>885</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="F34" s="7" t="s">
         <v>886</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>854</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>852</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="32.4">
       <c r="B35" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="E35" s="7" t="s">
         <v>888</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>1474</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>856</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>889</v>
-      </c>
       <c r="F35" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>890</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="D36" s="7" t="s">
+        <v>791</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>891</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>792</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>815</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="32.4">
       <c r="B37" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>893</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="D37" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>894</v>
       </c>
-      <c r="D37" s="7" t="s">
-        <v>850</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>895</v>
-      </c>
       <c r="F37" s="7" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="38" spans="2:8" ht="32.4">
       <c r="B38" s="7" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C38" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>896</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="E38" s="7" t="s">
         <v>897</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="F38" s="7" t="s">
         <v>898</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="39" spans="2:8" ht="32.4">
       <c r="B39" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>900</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="D39" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="E39" s="7" t="s">
         <v>901</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>839</v>
-      </c>
-      <c r="E39" s="7" t="s">
+      <c r="F39" s="7" t="s">
         <v>902</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="32.4">
       <c r="B40" s="7" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C40" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>873</v>
       </c>
-      <c r="D40" s="7" t="s">
-        <v>874</v>
-      </c>
       <c r="E40" s="7" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="8" t="s">
+        <v>904</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>814</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>890</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>905</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>792</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>815</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>891</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="32.4">
       <c r="B42" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="32.4">
       <c r="B43" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C43" s="7" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>1281</v>
       </c>
-      <c r="D43" s="7" t="s">
-        <v>847</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>1282</v>
-      </c>
       <c r="F43" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="32.4">
       <c r="B44" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C44" s="7" t="s">
+        <v>915</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>916</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>1271</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>917</v>
-      </c>
       <c r="F44" s="7" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="32.4">
       <c r="B45" s="7" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>1250</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="D45" s="7" t="s">
+        <v>923</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>1251</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>924</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>1252</v>
-      </c>
       <c r="F45" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="32.4">
       <c r="B46" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="32.4">
       <c r="B47" s="7" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>1254</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>1255</v>
-      </c>
       <c r="D47" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="E47" s="7" t="s">
+        <v>910</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>911</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>912</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
     </row>
     <row r="48" spans="2:8" ht="32.4">
       <c r="B48" s="7" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
     </row>
     <row r="49" spans="2:8" ht="32.4">
       <c r="B49" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
     </row>
     <row r="50" spans="2:8" ht="32.4">
       <c r="B50" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
     <row r="51" spans="2:8" ht="32.4">
       <c r="B51" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
     </row>
     <row r="52" spans="2:8" ht="32.4">
       <c r="B52" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C52" s="7" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>912</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="F52" s="7" t="s">
         <v>1275</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>913</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>926</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>1276</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
     </row>
     <row r="53" spans="2:8" ht="32.4">
       <c r="B53" s="7" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="E53" s="7" t="s">
         <v>1262</v>
       </c>
-      <c r="C53" s="7" t="s">
-        <v>1477</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>917</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>1263</v>
-      </c>
       <c r="F53" s="7" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
     </row>
     <row r="54" spans="2:8" ht="32.4">
       <c r="B54" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
     </row>
     <row r="55" spans="2:8" ht="32.4">
       <c r="B55" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D55" s="7" t="s">
+        <v>918</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="F55" s="7" t="s">
         <v>919</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>917</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>920</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
     </row>
     <row r="56" spans="2:8" ht="32.4">
       <c r="B56" s="7" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="F56" s="7" t="s">
         <v>1266</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>867</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>1503</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>832</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>1267</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
     </row>
     <row r="57" spans="2:8" ht="32.4">
       <c r="B57" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
     </row>
     <row r="58" spans="2:8" ht="32.4">
       <c r="B58" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C58" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>926</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>927</v>
-      </c>
       <c r="E58" s="7" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
     </row>
     <row r="59" spans="2:8" ht="32.4">
       <c r="B59" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="E59" s="7" t="s">
+        <v>922</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>923</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>924</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
     </row>
     <row r="60" spans="2:8" ht="32.4">
       <c r="B60" s="7" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
@@ -12826,19 +12843,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>1041</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>1042</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>1043</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>1044</v>
-      </c>
       <c r="F2" s="7" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -12846,19 +12863,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>1045</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>1046</v>
-      </c>
       <c r="D3" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -12866,19 +12883,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>1049</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>1050</v>
-      </c>
       <c r="D4" s="7" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="32.4">
@@ -12886,19 +12903,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G5" s="3"/>
     </row>
@@ -12907,19 +12924,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>1058</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>1059</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>1347</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>1060</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="G6" s="3"/>
     </row>
@@ -12928,19 +12945,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>1061</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>1509</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>1043</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>1062</v>
       </c>
       <c r="G7" s="3"/>
     </row>
@@ -12949,19 +12966,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>1063</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>1064</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="32.4">
@@ -12969,19 +12986,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="32.4">
@@ -12989,19 +13006,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>1067</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>1068</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -13009,19 +13026,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>1069</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>1513</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>1504</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>1070</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -13029,19 +13046,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>1514</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>1370</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>1515</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="32.4">
@@ -13049,19 +13066,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="E13" s="7" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>1074</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="32.4">
@@ -13069,19 +13086,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>1076</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>1514</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>1354</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>1077</v>
-      </c>
       <c r="F14" s="7" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -13089,19 +13106,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.4">
@@ -13109,19 +13126,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="32.4">
@@ -13129,19 +13146,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="32.4">
@@ -13149,19 +13166,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -13169,19 +13186,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>1084</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>1508</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="32.4">
@@ -13189,19 +13206,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="32.4">
@@ -13209,19 +13226,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="32.4">
@@ -13229,19 +13246,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="32.4">
@@ -13249,19 +13266,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>1096</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>1508</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="32.4">
@@ -13269,19 +13286,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>1098</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="D24" s="7" t="s">
         <v>1099</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>1100</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="F24" s="7" t="s">
         <v>1101</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="32.4">
@@ -13289,19 +13306,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>1373</v>
-      </c>
-      <c r="E25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>1055</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="32.4">
@@ -13309,19 +13326,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -13329,19 +13346,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>1105</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>797</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>1055</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -13349,19 +13366,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="32.4">
@@ -13369,19 +13386,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="32.4">
@@ -13389,19 +13406,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -13409,19 +13426,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>1349</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>1110</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>1350</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -13429,19 +13446,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="32.4">
@@ -13449,19 +13466,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>1113</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>1353</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>1354</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>1114</v>
       </c>
       <c r="G33" s="7"/>
     </row>
@@ -13470,19 +13487,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="32.4">
@@ -13490,19 +13507,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="H35" s="7"/>
     </row>
@@ -13511,19 +13528,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -13531,19 +13548,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>1119</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>1378</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="32.4">
@@ -13551,19 +13568,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>1121</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>797</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -13571,19 +13588,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="32.4">
@@ -13591,19 +13608,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="10" customFormat="1">
@@ -13611,19 +13628,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>1125</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="D41" s="8" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>1126</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E41" s="8" t="s">
+      <c r="F41" s="8" t="s">
         <v>1127</v>
-      </c>
-      <c r="F41" s="8" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="32.4">
@@ -13631,19 +13648,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F42" s="7" t="s">
         <v>1129</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>1375</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>1374</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>1520</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="32.4">
@@ -13651,19 +13668,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>1131</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>1376</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="32.4">
@@ -13671,19 +13688,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C44" s="7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>1133</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="F44" s="7" t="s">
         <v>1362</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>1363</v>
       </c>
       <c r="G44" s="3"/>
     </row>
@@ -13692,19 +13709,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>1135</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>1379</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>1136</v>
       </c>
       <c r="G45" s="3"/>
     </row>
@@ -13713,19 +13730,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F46" s="7" t="s">
         <v>1137</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>1358</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>1087</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>1379</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>1138</v>
       </c>
       <c r="G46" s="3"/>
     </row>
@@ -13734,19 +13751,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>1139</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="D47" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>1140</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>1377</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>1141</v>
       </c>
       <c r="G47" s="3"/>
     </row>
@@ -13755,19 +13772,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>1142</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="D48" s="7" t="s">
         <v>1143</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="E48" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>1144</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>1145</v>
       </c>
       <c r="G48" s="3"/>
     </row>
@@ -13776,19 +13793,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>1146</v>
       </c>
-      <c r="C49" s="7" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D49" s="7" t="s">
+      <c r="E49" s="7" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>1147</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>1521</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>1148</v>
       </c>
       <c r="G49" s="3"/>
     </row>
@@ -13797,19 +13814,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F50" s="7" t="s">
         <v>1149</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>1515</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>1150</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -13819,19 +13836,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>1151</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>1092</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>1152</v>
-      </c>
       <c r="F51" s="7" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H51" s="3"/>
     </row>
@@ -13840,19 +13857,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D52" s="7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F52" s="7" t="s">
         <v>1381</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>1055</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>1382</v>
       </c>
       <c r="H52" s="3"/>
     </row>
@@ -13861,19 +13878,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="H53" s="3"/>
     </row>
@@ -13882,19 +13899,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>1154</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>1155</v>
-      </c>
       <c r="F54" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H54" s="3"/>
     </row>
@@ -13903,19 +13920,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="D55" s="7" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E55" s="7" t="s">
         <v>1158</v>
       </c>
-      <c r="E55" s="7" t="s">
+      <c r="F55" s="7" t="s">
         <v>1159</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>1160</v>
       </c>
       <c r="H55" s="3"/>
     </row>
@@ -13924,19 +13941,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F56" s="7" t="s">
         <v>1161</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>1162</v>
       </c>
       <c r="H56" s="3"/>
     </row>
@@ -13945,19 +13962,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="C57" s="7" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>1164</v>
-      </c>
       <c r="F57" s="7" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H57" s="3"/>
     </row>
@@ -13966,19 +13983,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>1520</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="C58" s="7" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>1521</v>
-      </c>
-      <c r="E58" s="7" t="s">
+      <c r="F58" s="7" t="s">
         <v>1166</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>1167</v>
       </c>
       <c r="H58" s="3"/>
     </row>
@@ -13987,19 +14004,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="D59" s="7" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>1169</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>1374</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>1157</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="32.4">
@@ -14007,19 +14024,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C60" s="7" t="s">
         <v>1171</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="D60" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="D60" s="7" t="s">
+      <c r="E60" s="7" t="s">
         <v>1173</v>
       </c>
-      <c r="E60" s="7" t="s">
+      <c r="F60" s="7" t="s">
         <v>1174</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="32.4">
@@ -14027,19 +14044,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>1176</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>1517</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>1375</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>1381</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>1177</v>
       </c>
     </row>
   </sheetData>
@@ -14083,1021 +14100,1021 @@
     </row>
     <row r="2" spans="1:6" ht="32.4">
       <c r="B2" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>934</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
+        <v>921</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>935</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>922</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>936</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="32.4">
       <c r="B3" s="7" t="s">
+        <v>937</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>938</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>939</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>940</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>941</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="32.4">
       <c r="B4" s="7" t="s">
+        <v>942</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>943</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>944</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>921</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
         <v>945</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="32.4">
       <c r="B5" s="7" t="s">
+        <v>946</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>947</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>948</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>949</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>950</v>
-      </c>
       <c r="F5" s="7" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="32.4">
       <c r="B6" s="7" t="s">
+        <v>950</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>951</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>952</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>953</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>954</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32.4">
       <c r="B7" s="7" t="s">
+        <v>955</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>956</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
+        <v>920</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>957</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>921</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>958</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="32.4">
       <c r="B8" s="7" t="s">
+        <v>959</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>960</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
         <v>961</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="32.4">
       <c r="B9" s="7" t="s">
+        <v>962</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>963</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>964</v>
-      </c>
       <c r="D9" s="7" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="32.4">
       <c r="B10" s="7" t="s">
+        <v>964</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>965</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>962</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>964</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32.4">
       <c r="B11" s="7" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>935</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>936</v>
-      </c>
       <c r="E11" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="32.4">
       <c r="B12" s="7" t="s">
+        <v>967</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>968</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>969</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="32.4">
       <c r="B13" s="7" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="32.4">
       <c r="B14" s="7" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="32.4">
       <c r="B15" s="7" t="s">
+        <v>972</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>973</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>945</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>974</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>975</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="32.4">
       <c r="B16" s="7" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="32.4">
       <c r="B17" s="7" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="32.4">
       <c r="B18" s="7" t="s">
+        <v>978</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>958</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="F18" s="7" t="s">
         <v>979</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>959</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="32.4">
       <c r="B19" s="7" t="s">
+        <v>980</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>981</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>945</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>1223</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>964</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="32.4">
       <c r="B20" s="7" t="s">
+        <v>982</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>983</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>935</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="32.4">
       <c r="B21" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>953</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>960</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>985</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>954</v>
-      </c>
-      <c r="D21" s="9" t="s">
-        <v>961</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>936</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="32.4">
       <c r="B22" s="7" t="s">
+        <v>986</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>938</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>987</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="E22" s="7" t="s">
         <v>939</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="F22" s="7" t="s">
         <v>988</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>940</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="32.4">
       <c r="B23" s="7" t="s">
+        <v>989</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>952</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>990</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>953</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>991</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="32.4">
       <c r="B24" s="7" t="s">
+        <v>992</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>973</v>
+      </c>
+      <c r="F24" s="7" t="s">
         <v>993</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>964</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>1215</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>974</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="32.4">
       <c r="B25" s="7" t="s">
+        <v>994</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>995</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>996</v>
-      </c>
       <c r="D25" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="26" spans="2:6" ht="32.4">
       <c r="B26" s="7" t="s">
+        <v>996</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>960</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="F26" s="7" t="s">
         <v>997</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>961</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>964</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="27" spans="2:6" ht="32.4">
       <c r="B27" s="7" t="s">
+        <v>998</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>999</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="D27" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>1000</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="28" spans="2:6" ht="32.4">
       <c r="B28" s="7" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>947</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>1002</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>948</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>1221</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="29" spans="2:6" ht="32.4">
       <c r="B29" s="7" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="30" spans="2:6" ht="32.4">
       <c r="B30" s="7" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="F30" s="7" t="s">
         <v>1005</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="31" spans="2:6" ht="32.4">
       <c r="B31" s="7" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>1007</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>1220</v>
-      </c>
-      <c r="D31" s="7" t="s">
+      <c r="E31" s="7" t="s">
+        <v>954</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>1008</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>955</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="7" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F32" s="7" t="s">
         <v>1213</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>975</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="32.4">
       <c r="B33" s="7" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H33" s="7"/>
     </row>
     <row r="34" spans="2:9" ht="32.4">
       <c r="B34" s="7" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>1210</v>
-      </c>
       <c r="E34" s="7" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H34" s="7"/>
     </row>
     <row r="35" spans="2:9" ht="32.4">
       <c r="B35" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>963</v>
+      </c>
+      <c r="F35" s="7" t="s">
         <v>1013</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>964</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>1014</v>
       </c>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
     </row>
     <row r="36" spans="2:9" ht="32.4">
       <c r="B36" s="7" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>1015</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="D36" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>939</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>1016</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>942</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>940</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>1017</v>
       </c>
       <c r="I36" s="7"/>
     </row>
     <row r="37" spans="2:9" ht="32.4">
       <c r="B37" s="7" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>1018</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>1019</v>
       </c>
       <c r="I37" s="7"/>
     </row>
     <row r="38" spans="2:9" ht="32.4">
       <c r="B38" s="7" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E38" s="7" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F38" s="7" t="s">
         <v>1022</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>1023</v>
       </c>
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="2:9" ht="32.4">
       <c r="B39" s="7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>935</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>953</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="F39" s="7" t="s">
         <v>1024</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>936</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>1025</v>
       </c>
       <c r="I39" s="7"/>
     </row>
     <row r="40" spans="2:9" ht="32.4">
       <c r="B40" s="7" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C40" s="7" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>944</v>
+      </c>
+      <c r="F40" s="7" t="s">
         <v>1216</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>1219</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>945</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>1217</v>
       </c>
       <c r="I40" s="7"/>
     </row>
     <row r="41" spans="2:9" ht="32.4">
       <c r="B41" s="8" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>951</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>960</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>1027</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>952</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>953</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>961</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>1028</v>
       </c>
       <c r="I41" s="7"/>
     </row>
     <row r="42" spans="2:9" ht="32.4">
       <c r="B42" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="D42" s="7" t="s">
         <v>1179</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>1180</v>
-      </c>
       <c r="E42" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="I42" s="7"/>
     </row>
     <row r="43" spans="2:9" ht="32.4">
       <c r="B43" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C43" s="7" t="s">
         <v>1181</v>
       </c>
-      <c r="C43" s="7" t="s">
-        <v>1182</v>
-      </c>
       <c r="D43" s="7" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="I43" s="7"/>
     </row>
     <row r="44" spans="2:9" ht="32.4">
       <c r="B44" s="7" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>941</v>
+      </c>
+      <c r="E44" s="7" t="s">
         <v>1183</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="F44" s="7" t="s">
         <v>1235</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>942</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>1236</v>
       </c>
       <c r="I44" s="7"/>
     </row>
     <row r="45" spans="2:9" ht="32.4">
       <c r="B45" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="I45" s="7"/>
     </row>
     <row r="46" spans="2:9" ht="32.4">
       <c r="B46" s="7" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="I46" s="7"/>
     </row>
     <row r="47" spans="2:9" ht="32.4">
       <c r="B47" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>1188</v>
-      </c>
       <c r="D47" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="I47" s="7"/>
     </row>
     <row r="48" spans="2:9">
       <c r="B48" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C48" s="7" t="s">
         <v>1189</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>1190</v>
-      </c>
       <c r="D48" s="7" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="32.4">
       <c r="B49" s="7" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="50" spans="2:6" ht="32.4">
       <c r="B50" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C50" s="7" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>951</v>
+      </c>
+      <c r="F50" s="7" t="s">
         <v>1236</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>952</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="51" spans="2:6" ht="32.4">
       <c r="B51" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D51" s="7" t="s">
+      <c r="E51" s="7" t="s">
         <v>1194</v>
       </c>
-      <c r="E51" s="7" t="s">
-        <v>1195</v>
-      </c>
       <c r="F51" s="7" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="52" spans="2:6" ht="32.4">
       <c r="B52" s="7" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="53" spans="2:6" ht="32.4">
       <c r="B53" s="7" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E53" s="7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>1036</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="54" spans="2:6" ht="32.4">
       <c r="B54" s="7" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="55" spans="2:6" ht="32.4">
       <c r="B55" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>1199</v>
       </c>
-      <c r="C55" s="7" t="s">
-        <v>1227</v>
-      </c>
-      <c r="D55" s="7" t="s">
+      <c r="E55" s="7" t="s">
         <v>1200</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>1201</v>
-      </c>
       <c r="F55" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="7" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="57" spans="2:6" ht="32.4">
       <c r="B57" s="7" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E57" s="7" t="s">
         <v>1203</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="F57" s="7" t="s">
         <v>1239</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="7" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="59" spans="2:6" ht="32.4">
       <c r="B59" s="7" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="60" spans="2:6" ht="32.4">
       <c r="B60" s="7" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
   </sheetData>
@@ -15352,7 +15369,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>72</v>
@@ -15369,7 +15386,7 @@
         <v>602</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>47</v>
@@ -15389,13 +15406,13 @@
         <v>84</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>91</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -15406,10 +15423,10 @@
         <v>604</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>48</v>
@@ -15432,7 +15449,7 @@
         <v>87</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>589</v>
@@ -15463,19 +15480,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>72</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="32.4">
@@ -15489,7 +15506,7 @@
         <v>55</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>70</v>
@@ -15523,7 +15540,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>611</v>
+        <v>1521</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>87</v>
@@ -15532,10 +15549,10 @@
         <v>66</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>91</v>
+        <v>1523</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>84</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="32.4">
@@ -15543,7 +15560,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>163</v>
@@ -15563,7 +15580,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>188</v>
@@ -15583,7 +15600,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>184</v>
@@ -15592,7 +15609,7 @@
         <v>86</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>163</v>
@@ -15603,7 +15620,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>207</v>
@@ -15623,7 +15640,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>161</v>
@@ -15643,7 +15660,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>216</v>
@@ -15663,7 +15680,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>174</v>
@@ -15672,7 +15689,7 @@
         <v>211</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>196</v>
@@ -15683,7 +15700,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>167</v>
@@ -15703,7 +15720,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>196</v>
@@ -15723,7 +15740,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>174</v>
@@ -15732,7 +15749,7 @@
         <v>172</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>188</v>
@@ -15743,7 +15760,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>167</v>
@@ -15763,7 +15780,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>209</v>
@@ -15783,7 +15800,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>209</v>
@@ -15803,7 +15820,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>68</v>
@@ -15823,7 +15840,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>174</v>
@@ -15835,7 +15852,7 @@
         <v>196</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="32.4">
@@ -15843,7 +15860,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>102</v>
@@ -15863,7 +15880,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>188</v>
@@ -15883,7 +15900,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>216</v>
@@ -15895,7 +15912,7 @@
         <v>74</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="32.4">
@@ -15903,7 +15920,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>188</v>
@@ -15923,7 +15940,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>213</v>
@@ -15943,7 +15960,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>347</v>
@@ -15963,7 +15980,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>362</v>
@@ -15983,7 +16000,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>192</v>
@@ -16003,16 +16020,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>388</v>
       </c>
       <c r="D45" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>641</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>642</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>375</v>
@@ -16023,7 +16040,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>176</v>
@@ -16043,7 +16060,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>396</v>
@@ -16063,7 +16080,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>396</v>
@@ -16072,10 +16089,10 @@
         <v>362</v>
       </c>
       <c r="E48" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="F48" s="7" t="s">
         <v>646</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="32.4">
@@ -16083,13 +16100,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>648</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="D49" s="7" t="s">
         <v>649</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>650</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>360</v>
@@ -16103,13 +16120,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>362</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>394</v>
@@ -16123,7 +16140,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>396</v>
@@ -16143,7 +16160,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>360</v>
@@ -16152,7 +16169,7 @@
         <v>356</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>394</v>
@@ -16163,7 +16180,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>377</v>
@@ -16172,7 +16189,7 @@
         <v>100</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>364</v>
@@ -16183,13 +16200,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>204</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>58</v>
@@ -16203,7 +16220,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>349</v>
@@ -16223,7 +16240,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>192</v>
@@ -16243,13 +16260,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>176</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>78</v>
@@ -16263,13 +16280,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>385</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>565</v>
@@ -16283,7 +16300,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>194</v>
@@ -16303,16 +16320,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>663</v>
       </c>
-      <c r="C60" s="7" t="s">
-        <v>1366</v>
-      </c>
-      <c r="D60" s="7" t="s">
+      <c r="E60" s="7" t="s">
         <v>664</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>665</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>391</v>
@@ -16323,7 +16340,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>381</v>

--- a/expData.xlsx
+++ b/expData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\f\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41F2DFA-CCBF-486C-864F-54ABE18EC3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F650262-E1C7-4DFD-BAEA-49A465DDC976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2620" uniqueCount="1506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="1506">
   <si>
     <t>activeScence</t>
   </si>
@@ -5334,7 +5334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="3" max="3" width="17.6640625" customWidth="1"/>
@@ -5367,7 +5367,7 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -5384,7 +5384,7 @@
         <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>1490</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -5401,7 +5401,7 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -5425,11 +5425,6 @@
       </c>
       <c r="E5" s="4">
         <v>300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="C6" t="s">
-        <v>1490</v>
       </c>
     </row>
   </sheetData>

--- a/expData.xlsx
+++ b/expData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F650262-E1C7-4DFD-BAEA-49A465DDC976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B693872-7ED9-4E1D-8507-0363E408C50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2619" uniqueCount="1506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="1506">
   <si>
     <t>activeScence</t>
   </si>
@@ -7946,7 +7946,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B81D8F-FB0A-4661-BE07-500028C2F2D5}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="2" max="2" width="39.44140625" customWidth="1"/>
@@ -8096,17 +8096,125 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="B8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9" s="7"/>
-      <c r="F9" s="7"/>
+    <row r="8" spans="1:6" ht="32.4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="32.4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>1500</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="32.4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32.4">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="32.4">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>1496</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -8117,7 +8225,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B7F6CB-957F-4A76-AEA7-6CF767A6E72F}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8257,6 +8365,126 @@
         <v>1495</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="145.80000000000001">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="145.80000000000001">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="97.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="145.80000000000001">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="145.80000000000001">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="145.80000000000001">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>1496</v>
       </c>
     </row>
@@ -8268,7 +8496,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F07C16-A0CC-4D13-8397-D06012458C7A}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -8408,6 +8636,126 @@
         <v>1495</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="145.80000000000001">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="145.80000000000001">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="97.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="145.80000000000001">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="145.80000000000001">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="145.80000000000001">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1495</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>1496</v>
       </c>
     </row>

--- a/expData.xlsx
+++ b/expData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity_project\Corn_Game\camera\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B693872-7ED9-4E1D-8507-0363E408C50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F547A3C8-5B97-4B9D-B2EE-E1D00F99FC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="1506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2673" uniqueCount="1503">
   <si>
     <t>activeScence</t>
   </si>
@@ -4860,14 +4860,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>She was anxious about the results because the interview went badly.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>He tried to stay calm even though everyone was arguing loudly.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">She was anxious </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4909,10 +4901,6 @@
   </si>
   <si>
     <t>painful for his</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">The long walk in the rain was painful for his </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -7976,244 +7964,220 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="32.4">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" t="s">
         <v>1491</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E2" t="s">
         <v>1493</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="32.4">
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>1492</v>
-      </c>
+      <c r="B3" s="7"/>
       <c r="C3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E3" t="s">
         <v>1497</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" s="7" t="s">
         <v>1498</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>1504</v>
-      </c>
+      <c r="B4" s="7"/>
       <c r="C4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E4" t="s">
         <v>1501</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" s="7" t="s">
         <v>1502</v>
       </c>
-      <c r="E4" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="32.4">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" t="s">
         <v>1491</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E5" t="s">
         <v>1493</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E5" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="32.4">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" t="s">
         <v>1491</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E6" t="s">
         <v>1493</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E6" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="32.4">
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" t="s">
         <v>1491</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E7" t="s">
         <v>1493</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E7" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="32.4">
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" t="s">
         <v>1491</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E8" t="s">
         <v>1493</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E8" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="32.4">
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>1492</v>
-      </c>
+      <c r="B9" s="7"/>
       <c r="C9" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E9" t="s">
         <v>1497</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" s="7" t="s">
         <v>1498</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>1504</v>
-      </c>
+      <c r="B10" s="7"/>
       <c r="C10" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E10" t="s">
         <v>1501</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" s="7" t="s">
         <v>1502</v>
       </c>
-      <c r="E10" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="32.4">
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" t="s">
         <v>1491</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E11" t="s">
         <v>1493</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E11" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="32.4">
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" t="s">
         <v>1491</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E12" t="s">
         <v>1493</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E12" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="32.4">
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" t="s">
         <v>1491</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E13" t="s">
         <v>1493</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" s="7" t="s">
         <v>1494</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -8248,244 +8212,220 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="145.80000000000001">
+    <row r="2" spans="1:6" ht="48.6">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" t="s">
         <v>1491</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E2" t="s">
         <v>1493</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="3" spans="1:6" ht="32.4">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>1492</v>
-      </c>
+      <c r="B3" s="7"/>
       <c r="C3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E3" t="s">
         <v>1497</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" s="7" t="s">
         <v>1498</v>
       </c>
-      <c r="E3" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="97.2">
+    </row>
+    <row r="4" spans="1:6" ht="32.4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>1504</v>
-      </c>
+      <c r="B4" s="7"/>
       <c r="C4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E4" t="s">
         <v>1501</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" s="7" t="s">
         <v>1502</v>
       </c>
-      <c r="E4" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="5" spans="1:6" ht="48.6">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" t="s">
         <v>1491</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E5" t="s">
         <v>1493</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E5" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="6" spans="1:6" ht="48.6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" t="s">
         <v>1491</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E6" t="s">
         <v>1493</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E6" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="7" spans="1:6" ht="48.6">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" t="s">
         <v>1491</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E7" t="s">
         <v>1493</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E7" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="8" spans="1:6" ht="48.6">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" t="s">
         <v>1491</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E8" t="s">
         <v>1493</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E8" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="9" spans="1:6" ht="32.4">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>1492</v>
-      </c>
+      <c r="B9" s="7"/>
       <c r="C9" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E9" t="s">
         <v>1497</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" s="7" t="s">
         <v>1498</v>
       </c>
-      <c r="E9" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="97.2">
+    </row>
+    <row r="10" spans="1:6" ht="32.4">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>1504</v>
-      </c>
+      <c r="B10" s="7"/>
       <c r="C10" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E10" t="s">
         <v>1501</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" s="7" t="s">
         <v>1502</v>
       </c>
-      <c r="E10" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="11" spans="1:6" ht="48.6">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" t="s">
         <v>1491</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E11" t="s">
         <v>1493</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E11" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="12" spans="1:6" ht="48.6">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" t="s">
         <v>1491</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E12" t="s">
         <v>1493</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E12" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="13" spans="1:6" ht="48.6">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" t="s">
         <v>1491</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E13" t="s">
         <v>1493</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" s="7" t="s">
         <v>1494</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -8519,244 +8459,220 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="145.80000000000001">
+    <row r="2" spans="1:6" ht="48.6">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" t="s">
         <v>1491</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E2" t="s">
         <v>1493</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="3" spans="1:6" ht="32.4">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>1492</v>
-      </c>
+      <c r="B3" s="7"/>
       <c r="C3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E3" t="s">
         <v>1497</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" s="7" t="s">
         <v>1498</v>
       </c>
-      <c r="E3" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="97.2">
+    </row>
+    <row r="4" spans="1:6" ht="32.4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>1504</v>
-      </c>
+      <c r="B4" s="7"/>
       <c r="C4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E4" t="s">
         <v>1501</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" s="7" t="s">
         <v>1502</v>
       </c>
-      <c r="E4" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="5" spans="1:6" ht="48.6">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" t="s">
         <v>1491</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E5" t="s">
         <v>1493</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E5" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="6" spans="1:6" ht="48.6">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" t="s">
         <v>1491</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E6" t="s">
         <v>1493</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E6" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="7" spans="1:6" ht="48.6">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" t="s">
         <v>1491</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E7" t="s">
         <v>1493</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E7" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="8" spans="1:6" ht="48.6">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" t="s">
         <v>1491</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E8" t="s">
         <v>1493</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E8" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="9" spans="1:6" ht="32.4">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>1492</v>
-      </c>
+      <c r="B9" s="7"/>
       <c r="C9" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1496</v>
+      </c>
+      <c r="E9" t="s">
         <v>1497</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" s="7" t="s">
         <v>1498</v>
       </c>
-      <c r="E9" t="s">
-        <v>1499</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="97.2">
+    </row>
+    <row r="10" spans="1:6" ht="32.4">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>1504</v>
-      </c>
+      <c r="B10" s="7"/>
       <c r="C10" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E10" t="s">
         <v>1501</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" s="7" t="s">
         <v>1502</v>
       </c>
-      <c r="E10" t="s">
-        <v>1503</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>1505</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="11" spans="1:6" ht="48.6">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" t="s">
         <v>1491</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E11" t="s">
         <v>1493</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E11" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="12" spans="1:6" ht="48.6">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" t="s">
         <v>1491</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E12" t="s">
         <v>1493</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" s="7" t="s">
         <v>1494</v>
       </c>
-      <c r="E12" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="145.80000000000001">
+    </row>
+    <row r="13" spans="1:6" ht="48.6">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" t="s">
         <v>1491</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E13" t="s">
         <v>1493</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" s="7" t="s">
         <v>1494</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1495</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>1496</v>
       </c>
     </row>
   </sheetData>
